--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_pre_QA_QC.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3212
+          <t xml:space="preserve">2922
 </t>
         </is>
       </c>
@@ -703,70 +703,61 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
+          <t xml:space="preserve">1897
 </t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>315644</t>
+          <t>31524447</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>429</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t xml:space="preserve">938
+</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v/>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v/>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="n">
         <v/>
       </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
+      <c r="R4" s="3" t="n">
+        <v/>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
@@ -781,13 +772,13 @@
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -799,13 +790,13 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">7129
 </t>
         </is>
       </c>
@@ -838,113 +829,111 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1254
+</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">908
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">796
+</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>8405</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">269
 </t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>22</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
@@ -955,13 +944,13 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -982,7 +971,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3091
+          <t xml:space="preserve">391
 </t>
         </is>
       </c>
@@ -1000,13 +989,13 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -1024,7 +1013,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -1036,81 +1025,79 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7110
+</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1371
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0602
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1110
-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">131
-</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1147
-</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">959
 </t>
         </is>
       </c>
@@ -1149,7 +1136,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -1167,12 +1154,13 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t xml:space="preserve">119
+</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J7" s="3" t="n">
@@ -1186,37 +1174,34 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>31</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>450</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
@@ -1232,13 +1217,13 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9190
+          <t xml:space="preserve">739909
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">498
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -1267,7 +1252,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
@@ -1294,7 +1279,8 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>263</t>
+          <t xml:space="preserve">263
+</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1305,40 +1291,39 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>385</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1348,25 +1333,24 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">780
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2714
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -1377,7 +1361,7 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -1401,13 +1385,12 @@
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -1440,30 +1423,30 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17497
+          <t xml:space="preserve">1497
 </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
+          <t xml:space="preserve">2139
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">732
 </t>
         </is>
       </c>
@@ -1472,30 +1455,27 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v/>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>5542</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1506,18 +1486,16 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>484212</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">826
-</t>
-        </is>
+          <t>4849124</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v/>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
@@ -1528,7 +1506,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -1540,25 +1518,25 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">9359
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
@@ -1597,39 +1575,44 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">110
+4244 3
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">184
+</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148 1
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="K10" s="3" t="n">
@@ -1637,8 +1620,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1649,7 +1631,8 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>230</t>
+          <t xml:space="preserve">230
+</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -1666,13 +1649,13 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
@@ -1683,18 +1666,16 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">761
-</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v/>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -1706,8 +1687,7 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
@@ -1736,7 +1716,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5095
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
@@ -1754,28 +1734,31 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">0290
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+</t>
+        </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -1784,57 +1767,64 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24242
+22
+144561919
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+1
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">902
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">263
+</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t>2663</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t xml:space="preserve">6
+741
+</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -1845,24 +1835,23 @@
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -1883,48 +1872,45 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5067
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">1939
 </t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">150
+</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v/>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
@@ -1933,14 +1919,12 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1117
-</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v/>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1950,7 +1934,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
@@ -1968,40 +1952,33 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
         <v/>
       </c>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">860
-</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">906
-</t>
-        </is>
+      <c r="T12" s="3" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v/>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>435</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -2011,10 +1988,8 @@
 </t>
         </is>
       </c>
-      <c r="Z12" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="Z12" s="3" t="n">
+        <v/>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -2039,68 +2014,68 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>253</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1813
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>144</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11916
-</t>
+          <t>441</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">136
+</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
@@ -2112,24 +2087,24 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">7289
 </t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>33</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
+          <t xml:space="preserve">1839
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
+          <t xml:space="preserve">866
 </t>
         </is>
       </c>
@@ -2139,18 +2114,20 @@
 </t>
         </is>
       </c>
-      <c r="V13" s="3" t="n">
-        <v/>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -2162,8 +2139,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2183,7 +2159,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2270
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
@@ -2195,60 +2171,58 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11813
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v/>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">157
+</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>132</t>
+          <t xml:space="preserve">118
+</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>448</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -2274,34 +2248,36 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1566
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>60</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -2312,7 +2288,7 @@
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2333,7 +2309,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2290
+          <t xml:space="preserve">6390
 </t>
         </is>
       </c>
@@ -2345,70 +2321,69 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">21182
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1815
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
+          <t xml:space="preserve">73721
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v/>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">216
+</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
+          <t xml:space="preserve">1301
 </t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t xml:space="preserve">133
+</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -2419,37 +2394,37 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1517
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3108
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -2461,13 +2436,13 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1670
+          <t xml:space="preserve">670
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -2488,25 +2463,24 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99941
+          <t xml:space="preserve">224
+7656
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -2518,34 +2492,34 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">395
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1398
-</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">599
-</t>
-        </is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v/>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -2554,19 +2528,16 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
-</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v/>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11918
+          <t xml:space="preserve">662
 </t>
         </is>
       </c>
@@ -2578,47 +2549,44 @@
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>773</t>
+          <t xml:space="preserve">77
+</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="U16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">609
-</t>
-        </is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v/>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">982
+          <t xml:space="preserve">3852
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8011
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>824</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3640
+          <t xml:space="preserve">3699
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>332</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2638,13 +2606,13 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4459
+          <t xml:space="preserve">22249
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -2665,104 +2633,111 @@
           <t>444</t>
         </is>
       </c>
-      <c r="H17" s="3" t="n">
-        <v/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2294
-</t>
+          <t>417</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">448
+          <t xml:space="preserve">4981
 </t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t xml:space="preserve">591
+</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>416</t>
+          <t xml:space="preserve">136
+</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9718
+          <t xml:space="preserve">48390
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">044
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">69
+1
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t xml:space="preserve">55
+2
+</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">462
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>847</t>
+          <t xml:space="preserve">63
+</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0196
+          <t xml:space="preserve">2399
 </t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1161
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -2789,45 +2764,50 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4556
-</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">459
+</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t xml:space="preserve">18941
+</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">77
+7648
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -2838,24 +2818,24 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>118</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1565
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
@@ -2870,54 +2850,58 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">2725
 </t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">485
+          <t xml:space="preserve">4562
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
+          <t xml:space="preserve">1238
+224
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">7979
+</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">22254
+224
+1111
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
-</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2937,19 +2921,20 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5311
+          <t xml:space="preserve">4556
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>409</t>
+          <t xml:space="preserve">166
+</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -2960,25 +2945,23 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">1724
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v/>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
@@ -2988,42 +2971,39 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1329
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>11320</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">084
 </t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>254</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
@@ -3040,7 +3020,7 @@
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -3051,18 +3031,18 @@
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>54</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -3088,25 +3068,26 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5311
+          <t xml:space="preserve">5319
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>043</t>
+          <t xml:space="preserve">193
+</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -3117,39 +3098,43 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">54
+2
+72
 </t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1335
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v/>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">038
+</t>
+        </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>430</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -3160,19 +3145,19 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -3183,36 +3168,38 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">405
+          <t xml:space="preserve">425
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">210
+</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
@@ -3238,86 +3225,92 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">72
+3894
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t xml:space="preserve">187
+</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">69
+</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">35
+</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">062
 </t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>256</t>
+          <t xml:space="preserve">256
+</t>
         </is>
       </c>
       <c r="R21" s="3" t="n">
@@ -3325,36 +3318,37 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">13938
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>482</t>
+          <t xml:space="preserve">784
+</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -3387,39 +3381,41 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4290
-</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1271
+</t>
+        </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">137
+</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -3431,28 +3427,29 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v/>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1841
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">998
 </t>
         </is>
       </c>
@@ -3482,12 +3479,12 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>49</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -3499,25 +3496,25 @@
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">505
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">12394
 </t>
         </is>
       </c>
@@ -3538,79 +3535,80 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23203
+          <t xml:space="preserve">2323
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9454
+          <t xml:space="preserve">944
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">759
+          <t xml:space="preserve">7594
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">406
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>128</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">063
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930
+          <t xml:space="preserve">998
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -3620,12 +3618,15 @@
 </t>
         </is>
       </c>
-      <c r="R23" s="3" t="n">
-        <v/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">781
+          <t xml:space="preserve">787
 </t>
         </is>
       </c>
@@ -3636,36 +3637,36 @@
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1067
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>8515</t>
+          <t xml:space="preserve">2156
+</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3415
+          <t xml:space="preserve">345
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">609
 </t>
         </is>
       </c>
@@ -3686,23 +3687,25 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4641
+          <t xml:space="preserve">464
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>323</t>
+          <t xml:space="preserve">264
+</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>561</t>
+          <t xml:space="preserve">113
+</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3714,60 +3717,65 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">405
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">421
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>425</t>
+          <t xml:space="preserve">625
+</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">618
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
+          <t xml:space="preserve">4930
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">631
 </t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
@@ -3784,7 +3792,7 @@
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11774
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
@@ -3796,24 +3804,26 @@
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>8315</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1683
-</t>
-        </is>
-      </c>
-      <c r="Z24" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">683
+</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -3833,80 +3843,78 @@
       <c r="C25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">4889
+49
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
+          <t xml:space="preserve">291
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v/>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>101</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9260
+          <t xml:space="preserve">986
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -3918,43 +3926,51 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>54</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4695
+          <t xml:space="preserve">495
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">17721
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">292575
+111979
+</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2122
+1
+1111919
+</t>
+        </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -3981,7 +3997,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3499
+          <t xml:space="preserve">3402
 </t>
         </is>
       </c>
@@ -3993,7 +4009,8 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">96
+</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -4010,18 +4027,19 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1016
+          <t xml:space="preserve">572
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t xml:space="preserve">37
+</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -4030,31 +4048,31 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">2107
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -4084,36 +4102,36 @@
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">1639
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t xml:space="preserve">550
+</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4133,20 +4151,19 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3902
+          <t xml:space="preserve">3402
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>414</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -4157,7 +4174,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -4169,13 +4186,12 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
@@ -4187,42 +4203,40 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v/>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9808
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -4240,31 +4254,33 @@
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">222
+11737
 </t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">78 277
+185
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -4290,125 +4306,125 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5133
+          <t xml:space="preserve">533
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>493</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">454
+</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>1243</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1229
+1554
+</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">680
+</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1133
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">680
-</t>
-        </is>
-      </c>
-      <c r="U28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="W28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1167
 </t>
         </is>
       </c>
@@ -4446,109 +4462,109 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5933
+          <t xml:space="preserve">533
 </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">969
+</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">270
 </t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1116
-</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1812
-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17909
-</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">960
-</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">270
-</t>
-        </is>
-      </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>183</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">478
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">4728
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
@@ -4558,7 +4574,7 @@
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -4570,13 +4586,13 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -4597,48 +4613,49 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22848
+          <t xml:space="preserve">2848
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>188</t>
+          <t xml:space="preserve">3226
+</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">5227
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
+          <t xml:space="preserve">678
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">791
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">369
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -4650,13 +4667,13 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -4668,8 +4685,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>48161</t>
         </is>
       </c>
       <c r="P30" s="3" t="n">
@@ -4689,35 +4705,37 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">844
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>344845</t>
+          <t xml:space="preserve">3148
+</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t xml:space="preserve">554
+</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">995
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -4729,7 +4747,7 @@
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">350
+          <t xml:space="preserve">359
 </t>
         </is>
       </c>
@@ -4750,25 +4768,24 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
-</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1312
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -4780,18 +4797,18 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -4800,7 +4817,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -4817,35 +4834,37 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>45161</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">044
+          <t xml:space="preserve">0691
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>416</t>
+          <t xml:space="preserve">226
+</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11793
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">1691
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -4863,25 +4882,26 @@
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">2
+</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4901,106 +4921,97 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
-</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">17574
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v/>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
+          <t xml:space="preserve">592
+</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v/>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>015</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t xml:space="preserve">970
+</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">044
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">2421
 </t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>221</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11169
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
-</t>
+          <t>421</t>
         </is>
       </c>
       <c r="U32" s="3" t="n">
@@ -5013,12 +5024,15 @@
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
@@ -5028,7 +5042,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -5049,119 +5063,121 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t xml:space="preserve">34971
+</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>231</t>
+          <t xml:space="preserve">242
+</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">702
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>177</t>
+          <t xml:space="preserve">114
+</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v/>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">982
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">2091
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">799
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>510</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -5173,13 +5189,13 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">700
+          <t xml:space="preserve">836
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -5200,20 +5216,19 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3491
+          <t xml:space="preserve">3299
 </t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -5224,26 +5239,23 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1656
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -5254,83 +5266,84 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1529
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">787
+</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">85820
 </t>
         </is>
       </c>
@@ -5357,141 +5370,142 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3299
+          <t xml:space="preserve">567
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">95
+</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">55
+</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1481
 </t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">026
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">238
+</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">5206
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">12787
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="Z35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
+          <t xml:space="preserve">685
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v/>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -5510,141 +5524,141 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5067
+          <t xml:space="preserve">535
 </t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1398
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">090
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t xml:space="preserve">146
+</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">685
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -5665,20 +5679,20 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5355
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">777
+1188414042
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -5689,111 +5703,126 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>511</t>
+          <t xml:space="preserve">614242
+149081
+</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">460
+          <t xml:space="preserve">7
+119019
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">650
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">4227
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">714531 7
+</t>
+        </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">753824
+9
+222
+11
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>255</t>
+          <t xml:space="preserve">1118185
+</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
+          <t xml:space="preserve">31694
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>5413</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1546
+          <t xml:space="preserve">646257
+121191
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">847
+</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">528
+          <t xml:space="preserve">3595
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">346
+          <t xml:space="preserve">3456
 </t>
         </is>
       </c>
@@ -5814,7 +5843,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22404
+          <t xml:space="preserve">4481
 </t>
         </is>
       </c>
@@ -5826,129 +5855,135 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">997
+          <t xml:space="preserve">947
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>676</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">460
+          <t xml:space="preserve">4690
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">521
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">650
+          <t xml:space="preserve">1309
 </t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>04317</t>
+          <t>198</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">742
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4920
+          <t xml:space="preserve">27
+727227
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">753824
+9
+222
+11
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>11515</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2164
+          <t xml:space="preserve">633
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">847
+          <t xml:space="preserve">122
+92
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3595
-</t>
-        </is>
-      </c>
-      <c r="Z38" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3456
+</t>
+        </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -5967,135 +6002,131 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42481
+          <t xml:space="preserve">5739
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">609
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">997
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">8
+</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">421
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>04317</t>
+          <t xml:space="preserve">4227
+</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>11515</t>
+          <t>731</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
-</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
+          <t xml:space="preserve">780
+</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="n">
+        <v/>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2164
+          <t xml:space="preserve">81556
+15252197
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">2227
+191
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">15 28
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">847
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7419
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
@@ -6121,19 +6152,21 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">357
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">29
+4
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>422</t>
+          <t xml:space="preserve">710
+</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -6144,102 +6177,106 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">1051
 </t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>403</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 0
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>9936</t>
+          <t xml:space="preserve">266
+</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>151</t>
+          <t xml:space="preserve">184
+</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">635
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11980
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t xml:space="preserve">137
+</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">555
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">883
 </t>
         </is>
       </c>
@@ -6251,7 +6288,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -6272,20 +6309,19 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4512
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>40131</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -6296,119 +6332,118 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1665
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t xml:space="preserve">59
+</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10611
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">86
+</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1571
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">972
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
+          <t xml:space="preserve">519
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">2227
+191
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">2142
 </t>
         </is>
       </c>
@@ -6429,24 +6464,29 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4512
+          <t xml:space="preserve">57244
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>232</t>
+          <t xml:space="preserve">272
+</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">2771
+28 1
+187
+215
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>489</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -6457,12 +6497,13 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">7128
+</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
@@ -6474,96 +6515,95 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>403</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5980
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">432
+5
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">220
 </t>
         </is>
       </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">559
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1613</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1893
+          <t xml:space="preserve">883
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8390
+          <t xml:space="preserve">589
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -6584,130 +6624,150 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5244
+          <t xml:space="preserve">66668446
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>232</t>
+          <t xml:space="preserve">22422
+</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>40131</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12597
-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1517
+</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7128
+</t>
+        </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">717774
+82
+</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">24127
+8
+242257
 </t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>438</t>
+          <t xml:space="preserve">1859957
+5
+13 2
+529
+</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">068
 </t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42529
+21222
+</t>
+        </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">222224
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">2222
 </t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>1633</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="n">
-        <v/>
+          <t>1613</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
-        </is>
-      </c>
-      <c r="Z43" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">589
+</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">352
+</t>
+        </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -6724,33 +6784,48 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n">
-        <v/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57244
+</t>
+        </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v/>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2771
+28 1
+187
+215
+</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">277
+0
+2644
+</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">662
+</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v/>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>434</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="J44" s="3" t="n">
@@ -6758,59 +6833,72 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">271
+</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
       </c>
       <c r="M44" s="3" t="n">
         <v/>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6231
+          <t xml:space="preserve">3
+21
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">2424622
+2224
+</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">70
+</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">21694
+</t>
+        </is>
+      </c>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">599
+</t>
+        </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">859
 </t>
         </is>
       </c>
@@ -6820,15 +6908,19 @@
 </t>
         </is>
       </c>
-      <c r="X44" s="3" t="n">
-        <v/>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
       </c>
       <c r="Y44" s="3" t="n">
         <v/>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t>351</t>
+          <t xml:space="preserve">352
+</t>
         </is>
       </c>
       <c r="AA44" s="3" t="inlineStr">
@@ -6848,7 +6940,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161109
+          <t xml:space="preserve">101979
 </t>
         </is>
       </c>
@@ -6877,50 +6969,54 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">149
+</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">440
+</t>
+        </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3880
+          <t xml:space="preserve">380
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -6930,47 +7026,47 @@
 </t>
         </is>
       </c>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">710
-</t>
-        </is>
+      <c r="R45" s="3" t="n">
+        <v/>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">42529
+21222
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2164
+          <t xml:space="preserve">547
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">222224
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8519
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X45" s="3" t="n">
         <v/>
       </c>
-      <c r="Y45" s="3" t="n">
-        <v/>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
       </c>
       <c r="Z45" s="3" t="n">
         <v/>
@@ -6992,15 +7088,21 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4778
-</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">478
+</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -7010,7 +7112,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1694
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -7028,36 +7130,37 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t xml:space="preserve">521
+</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
@@ -7069,31 +7172,30 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">549
+          <t xml:space="preserve">21694
 </t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114 70
+          <t xml:space="preserve">197 1
 </t>
         </is>
       </c>
@@ -7103,23 +7205,22 @@
 </t>
         </is>
       </c>
-      <c r="W46" s="3" t="n">
-        <v/>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="n">
         <v/>
       </c>
-      <c r="Z46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
+      <c r="Z46" s="3" t="n">
+        <v/>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_pre_QA_QC.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2922
+          <t xml:space="preserve">3912
 </t>
         </is>
       </c>
@@ -703,7 +703,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1897
+          <t xml:space="preserve">11817
 </t>
         </is>
       </c>
@@ -715,95 +715,108 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>31524447</t>
+          <t xml:space="preserve">35
+</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>429</t>
+          <t xml:space="preserve">49
+</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1199
+</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1238
+</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">11141
+</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
+          <t xml:space="preserve">5425
 </t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">222191
 </t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>411</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7129
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -829,42 +842,40 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">1269
 </t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>445</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>411</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1254
+          <t xml:space="preserve">2154
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -874,7 +885,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
@@ -889,7 +900,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">1908
 </t>
         </is>
       </c>
@@ -898,59 +909,55 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>82</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v/>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">11895
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">1805
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -971,13 +978,13 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
+          <t xml:space="preserve">3091
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
@@ -989,14 +996,13 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -1007,87 +1013,78 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v/>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7110
+          <t xml:space="preserve">14110
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1371
+          <t xml:space="preserve">1131
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0602
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
+          <t xml:space="preserve">1191
+</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v/>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v/>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t xml:space="preserve">17158
+</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
@@ -1097,13 +1094,13 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">959
+          <t xml:space="preserve">1950
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -1124,7 +1121,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2758
+          <t xml:space="preserve">12758
 </t>
         </is>
       </c>
@@ -1136,94 +1133,97 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">1239
+</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>450</t>
+          <t xml:space="preserve">1150
+</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>113</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>433</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">739909
+          <t xml:space="preserve">790
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1948
 </t>
         </is>
       </c>
@@ -1234,25 +1234,22 @@
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -1279,130 +1276,126 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>81</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t xml:space="preserve">158
+</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>408</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>4244</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v/>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">17180
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>8</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
+          <t xml:space="preserve">1760
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">1173
+</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -1423,90 +1416,100 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1497
+          <t xml:space="preserve">17497
 </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>12895</t>
+          <t>128491</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">558
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2139
+          <t xml:space="preserve">919
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
-</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">739
+</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17026
+</t>
+        </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">564
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">651
+          <t xml:space="preserve">551
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>4849124</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">14848
+</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">026
+</t>
+        </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">1015
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
+          <t xml:space="preserve">1859
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">1885
 </t>
         </is>
       </c>
@@ -1518,37 +1521,37 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">12333
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9359
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">1849
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4145
+          <t xml:space="preserve">141545
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
@@ -1575,43 +1578,40 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-4244 3
-</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
+          <t xml:space="preserve">1110
+</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v/>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t xml:space="preserve">204
+</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">12114
 </t>
         </is>
       </c>
@@ -1620,62 +1620,66 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t xml:space="preserve">1113
+</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">11110
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">1968
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">1015
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">1127
+</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">141671
+</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67
+</t>
+        </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -1687,17 +1691,21 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t xml:space="preserve">1182
+</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
-</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1829
+</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1510
+</t>
+        </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1716,142 +1724,122 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">15093
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
+          <t xml:space="preserve">1273
+</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v/>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0290
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v/>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="n">
         <v/>
       </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24242
-22
-144561919
-</t>
-        </is>
+      <c r="L11" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v/>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-1
-</t>
-        </is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v/>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">1042
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">12263
 </t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-741
-</t>
+          <t>401</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t xml:space="preserve">2221
+</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t xml:space="preserve">660
+</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -1872,59 +1860,68 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">13067
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t xml:space="preserve">1259
+</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1939
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">01450
+</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1948
+</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v/>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">59
-</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v/>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1187
+</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1219
+</t>
+        </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1934,13 +1931,13 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">1950
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -1952,44 +1949,53 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="S12" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T12" s="3" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v/>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1129
+</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>43</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
-        </is>
-      </c>
-      <c r="Z12" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">10920
+</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -2008,138 +2014,127 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3579
-</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+          <t xml:space="preserve">13579
+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v/>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">11813
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>44</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v/>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>441</t>
-        </is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v/>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">1836
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7289
-</t>
-        </is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v/>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>43</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1839
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">866
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">196
+</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">1886
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">1840
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">96
+</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2159,37 +2154,36 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">2270
 </t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">01532
 </t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">11813
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
@@ -2198,31 +2192,28 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
+          <t xml:space="preserve">2182
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v/>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">111820
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>448</t>
+          <t xml:space="preserve">148
+</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -2231,36 +2222,36 @@
 </t>
         </is>
       </c>
-      <c r="P14" s="3" t="n">
-        <v/>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1069
+</t>
+        </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">904
-</t>
-        </is>
+          <t xml:space="preserve">11266
+</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v/>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -2271,7 +2262,7 @@
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
@@ -2282,13 +2273,13 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">1950
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">818110
 </t>
         </is>
       </c>
@@ -2309,46 +2300,50 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6390
+          <t xml:space="preserve">16310
 </t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21182
+          <t xml:space="preserve">1101108
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">111815
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73721
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t xml:space="preserve">59
+</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -2359,79 +2354,75 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301
+          <t xml:space="preserve">1213
 </t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">1012
 </t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>255</t>
+          <t xml:space="preserve">2255
+</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="T15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">480
-</t>
-        </is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="n">
+        <v/>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">11165
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
@@ -2442,7 +2433,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -2463,130 +2454,143 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-7656
+          <t xml:space="preserve">22271
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>280</t>
+          <t xml:space="preserve">1280
+</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>4668</t>
+          <t xml:space="preserve">2568
+</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">712
+          <t xml:space="preserve">792
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">395
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">398
+</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">591
+</t>
+        </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v/>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">679
+</t>
+        </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">4398
+</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
+          <t xml:space="preserve">111910
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">7211
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="U16" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">3101
+</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1609
+</t>
+        </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3852
+          <t xml:space="preserve">9212
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">8019
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>824</t>
+          <t xml:space="preserve">1822
+</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3699
+          <t xml:space="preserve">13640
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2606,144 +2610,141 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22249
+          <t xml:space="preserve">2459
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">11815
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">1145
+</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>417</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4981
-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v/>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">591
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">1136
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48390
+          <t xml:space="preserve">1978
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">1074
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-1
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-2
+          <t xml:space="preserve">1155
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t xml:space="preserve">1620
+</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399
+          <t xml:space="preserve">11196
 </t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">1161
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">728
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -2764,50 +2765,45 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">459
+          <t xml:space="preserve">14358
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>22444</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18941
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
-7648
-</t>
-        </is>
+          <t xml:space="preserve">1130
+</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v/>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">33
+</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -2818,29 +2814,32 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">876
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1610
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
@@ -2850,57 +2849,54 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2725
+          <t xml:space="preserve">1723
 </t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">11154
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4562
+          <t xml:space="preserve">14060
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
-224
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7979
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22254
-224
-1111
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t xml:space="preserve">137910
+</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
@@ -2921,133 +2917,132 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4556
+          <t xml:space="preserve">15311
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1106
+</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12110
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17110
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1130
+</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>2611</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1180
+</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>1420</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1724
-</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79
-</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v/>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1329
-</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>11320</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">084
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1890
-</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="T19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">485
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="W19" s="3" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="X19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>1420</t>
-        </is>
-      </c>
-      <c r="Z19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -3068,7 +3063,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5319
+          <t xml:space="preserve">5922
 </t>
         </is>
       </c>
@@ -3080,62 +3075,57 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">12084
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-2
-72
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">17335
+</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">49
+</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">038
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
+          <t xml:space="preserve">188181
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v/>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
@@ -3143,56 +3133,48 @@
 </t>
         </is>
       </c>
-      <c r="P20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
+      <c r="P20" s="3" t="n">
+        <v/>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="R20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
+          <t xml:space="preserve">280
+</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v/>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>513</t>
+          <t xml:space="preserve">11513
+</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
+          <t xml:space="preserve">1405
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>924</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">122982
 </t>
         </is>
       </c>
@@ -3202,11 +3184,8 @@
 </t>
         </is>
       </c>
-      <c r="Z20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">76
-</t>
-        </is>
+      <c r="Z20" s="3" t="n">
+        <v/>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -3225,142 +3204,134 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-3894
+          <t xml:space="preserve">3824
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">2248
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>421</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">131
+</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v/>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">062
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v/>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">19310
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13938
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">1870
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -3381,7 +3352,8 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t xml:space="preserve">14290
+</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3390,72 +3362,68 @@
 </t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1271
-</t>
-        </is>
+      <c r="E22" s="3" t="n">
+        <v/>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v/>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">1122
+</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -3467,54 +3435,53 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">11949
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>4434544</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>448</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">1225
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">20139
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">505
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12394
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
@@ -3535,138 +3502,133 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2323
+          <t xml:space="preserve">232031
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>132</t>
+          <t xml:space="preserve">1321
+</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">944
+          <t xml:space="preserve">949
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7594
+          <t xml:space="preserve">7509
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">406
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">063
+          <t xml:space="preserve">1013
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v/>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
+          <t xml:space="preserve">24930
+</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v/>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">11289
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
+          <t xml:space="preserve">781
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>23571</t>
+          <t xml:space="preserve">2357
+</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">1885
+</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">11067
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2156
+          <t xml:space="preserve">1855
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">345
+          <t xml:space="preserve">13415
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">609
+          <t xml:space="preserve">1410
 </t>
         </is>
       </c>
@@ -3687,7 +3649,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">464
+          <t xml:space="preserve">4841
 </t>
         </is>
       </c>
@@ -3705,124 +3667,120 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">1151
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">405
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">291
+</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
+          <t xml:space="preserve">761
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v/>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
+          <t xml:space="preserve">1124
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v/>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4930
+          <t xml:space="preserve">986
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">631
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>252</t>
+          <t xml:space="preserve">258
+</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>441</t>
+          <t xml:space="preserve">12479
+</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">11975
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">913
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>8315</t>
+          <t>411</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
+          <t xml:space="preserve">1689
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3842,141 +3800,125 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4889
-49
+          <t xml:space="preserve">14889
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+          <t xml:space="preserve">1259
+</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v/>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>1147</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">871
-</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v/>
       </c>
       <c r="J25" s="3" t="n">
         <v/>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t xml:space="preserve">11079
+</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">986
-</t>
-        </is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v/>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
+          <t xml:space="preserve">5493
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17721
+          <t xml:space="preserve">11518
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292575
-111979
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2122
-1
-1111919
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">660
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">816
 </t>
         </is>
       </c>
@@ -3997,13 +3939,13 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3402
+          <t xml:space="preserve">13499
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -4015,8 +3957,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -4027,42 +3968,39 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2107
-</t>
-        </is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v/>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
+          <t xml:space="preserve">1182
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v/>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
@@ -4070,11 +4008,8 @@
 </t>
         </is>
       </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
+      <c r="P26" s="3" t="n">
+        <v/>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
@@ -4084,54 +4019,54 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>45474</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">635
+          <t xml:space="preserve">1635
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t xml:space="preserve">216
+</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1639
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">1118
+</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4157,59 +4092,53 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
+          <t xml:space="preserve">1111
+</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v/>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
+          <t xml:space="preserve">111440
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v/>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">1151
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>424</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1122
 </t>
         </is>
       </c>
@@ -4222,65 +4151,60 @@
 </t>
         </is>
       </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
+      <c r="P27" s="3" t="n">
+        <v/>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">11618
 </t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">1860
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-11737
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78 277
-185
+          <t xml:space="preserve">11875
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
@@ -4306,43 +4230,42 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">533
+          <t xml:space="preserve">151395
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">11115
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">454
+          <t xml:space="preserve">11545
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -4353,37 +4276,36 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t xml:space="preserve">1134
+</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">11133
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-1554
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -4395,24 +4317,25 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">1186
+</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">680
+          <t xml:space="preserve">1680
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -4422,21 +4345,15 @@
 </t>
         </is>
       </c>
-      <c r="W28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="X28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
+      <c r="W28" s="3" t="n">
+        <v/>
+      </c>
+      <c r="X28" s="3" t="n">
+        <v/>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
@@ -4462,67 +4379,67 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">533
+          <t xml:space="preserve">5233
 </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>121</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v/>
+          <t>4841</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">09105
 </t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">11224
 </t>
         </is>
       </c>
@@ -4534,37 +4451,36 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">2270
 </t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>183</t>
+          <t xml:space="preserve">11817
+</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4728
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+          <t xml:space="preserve">478
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v/>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
@@ -4572,27 +4488,21 @@
 </t>
         </is>
       </c>
-      <c r="W29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="X29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
+      <c r="W29" s="3" t="n">
+        <v/>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v/>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">1600
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
@@ -4613,83 +4523,85 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2848
+          <t xml:space="preserve">228481
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3226
+          <t xml:space="preserve">1312
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5227
+          <t xml:space="preserve">1529
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">678
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">791
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">369
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">11195
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">522
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">561
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">659
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>48161</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">14890
+</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
@@ -4705,7 +4617,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">1844
 </t>
         </is>
       </c>
@@ -4717,37 +4629,37 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">554
+          <t xml:space="preserve">559
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">995
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3650
+          <t xml:space="preserve">13650
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">359
+          <t xml:space="preserve">350
 </t>
         </is>
       </c>
@@ -4768,7 +4680,8 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>4510</t>
+          <t xml:space="preserve">14520
+</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -4779,13 +4692,13 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">1104
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
@@ -4797,18 +4710,16 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
+          <t xml:space="preserve">721
+</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v/>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">391
 </t>
         </is>
       </c>
@@ -4817,7 +4728,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
@@ -4827,20 +4738,18 @@
 </t>
         </is>
       </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="N31" s="3" t="n">
+        <v/>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0691
+          <t xml:space="preserve">8404
 </t>
         </is>
       </c>
@@ -4852,55 +4761,55 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">21793
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1691
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">630
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">19 9
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">730 0
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
@@ -4921,86 +4830,94 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t xml:space="preserve">5208
+</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>229</t>
+          <t xml:space="preserve">279
+</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">11102
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17574
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">22177
+</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">37
+</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">612
+</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>015</t>
+          <t xml:space="preserve">110905
+</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v/>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2421
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t xml:space="preserve">1182
+</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -5011,7 +4928,8 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>421</t>
+          <t xml:space="preserve">1625
+</t>
         </is>
       </c>
       <c r="U32" s="3" t="n">
@@ -5019,32 +4937,30 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t xml:space="preserve">20214
+</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">700
-</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
+          <t xml:space="preserve">709
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v/>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -5063,7 +4979,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34971
+          <t xml:space="preserve">3491
 </t>
         </is>
       </c>
@@ -5075,32 +4991,28 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">702
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>4854</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">121114
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v/>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -5108,53 +5020,46 @@
 </t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
+      <c r="K33" s="3" t="n">
+        <v/>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="n">
         <v/>
       </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
+      <c r="N33" s="3" t="n">
+        <v/>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">982
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>438</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
@@ -5166,36 +5071,29 @@
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v/>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v/>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -5216,7 +5114,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3299
+          <t xml:space="preserve">3291
 </t>
         </is>
       </c>
@@ -5228,59 +5126,57 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>443</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">1141
+</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1529
-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1291
-</t>
-        </is>
+          <t xml:space="preserve">1159
+</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v/>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
@@ -5290,66 +5186,64 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">1218
+</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">11818
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">728
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">112871
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v/>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85820
+          <t xml:space="preserve">8930
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -5370,7 +5264,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
+          <t xml:space="preserve">15067
 </t>
         </is>
       </c>
@@ -5382,19 +5276,18 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">21540
 </t>
         </is>
       </c>
@@ -5411,45 +5304,37 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>515</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1481
-</t>
-        </is>
+          <t xml:space="preserve">1129
+</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v/>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">026
-</t>
-        </is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v/>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
@@ -5459,7 +5344,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">11476
 </t>
         </is>
       </c>
@@ -5471,41 +5356,44 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5206
+          <t xml:space="preserve">5720
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t xml:space="preserve">5162
+</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12787
+          <t xml:space="preserve">141168
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">685
-</t>
-        </is>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v/>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -5524,37 +5412,38 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">535
+          <t xml:space="preserve">5355
 </t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">2563
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">009
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1398
+          <t xml:space="preserve">1813
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t xml:space="preserve">64
+</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -5571,48 +5460,45 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">11016
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
+          <t xml:space="preserve">11105
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v/>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>255</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">1711
 </t>
         </is>
       </c>
@@ -5624,13 +5510,14 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">6850
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">1279
+</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
@@ -5641,24 +5528,25 @@
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t xml:space="preserve">1138
+</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">11108
 </t>
         </is>
       </c>
@@ -5679,45 +5567,41 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">22404
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">777
-1188414042
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t xml:space="preserve">1609
+</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">9917
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">614242
-149081
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-119019
+          <t xml:space="preserve">1460
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1161
 </t>
         </is>
       </c>
@@ -5729,88 +5613,78 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">650
-</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4227
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">714531 7
-</t>
-        </is>
+          <t xml:space="preserve">1650
+</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v/>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">24920
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">753824
-9
-222
-11
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118185
+          <t xml:space="preserve">1155
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31694
+          <t xml:space="preserve">2169
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t xml:space="preserve">545
+</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">11009
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">646257
-121191
+          <t xml:space="preserve">1831
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">847
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -5822,7 +5696,7 @@
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3456
+          <t xml:space="preserve">3946
 </t>
         </is>
       </c>
@@ -5843,36 +5717,37 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4481
+          <t xml:space="preserve">24481
 </t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">11122
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">947
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>676</t>
+          <t xml:space="preserve">11351
+</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4690
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -5884,64 +5759,50 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+          <t xml:space="preserve">5921
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v/>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1309
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">742
-</t>
-        </is>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v/>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-727227
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">753824
-9
-222
-11
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>1155</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="S38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="3" t="n">
+        <v/>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
@@ -5951,37 +5812,36 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-92
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3456
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
@@ -6002,19 +5862,20 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5739
+          <t xml:space="preserve">35999
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t xml:space="preserve">711180
+</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -6023,116 +5884,103 @@
 </t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70
-</t>
-        </is>
+      <c r="G39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v/>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t xml:space="preserve">108
+</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4227
-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v/>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">19808
 </t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">184
+</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>731</t>
+          <t xml:space="preserve">266
+</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
-</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81556
-15252197
+          <t xml:space="preserve">17200
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2227
-191
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15 28
+          <t xml:space="preserve">181517
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">21196
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t xml:space="preserve">760
+</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6152,20 +6000,19 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">357
+          <t xml:space="preserve">3351
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-4
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -6177,64 +6024,61 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v/>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">100
+</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1051
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
+          <t xml:space="preserve">1103
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v/>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">10
+</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
@@ -6246,43 +6090,40 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">635
+          <t xml:space="preserve">692
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="n">
+        <v/>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">0168
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
+          <t xml:space="preserve">21993
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
+          <t xml:space="preserve">9830
 </t>
         </is>
       </c>
@@ -6309,7 +6150,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">2454512
 </t>
         </is>
       </c>
@@ -6321,24 +6162,25 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>40131</t>
+          <t xml:space="preserve">82
+</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">112813
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">1510
 </t>
         </is>
       </c>
@@ -6348,102 +6190,88 @@
 </t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr">
+      <c r="J41" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 185
+</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">882
-</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">972
-</t>
-        </is>
+      <c r="P41" s="3" t="n">
+        <v/>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">57179
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="T41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">519
-</t>
-        </is>
+          <t xml:space="preserve">72166
+</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v/>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2227
-191
+          <t xml:space="preserve">1127
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">12220
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X41" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="n">
+        <v/>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2142
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
@@ -6464,40 +6292,34 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57244
-</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
+          <t xml:space="preserve">5244
+</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v/>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2771
-28 1
-187
-215
+          <t xml:space="preserve">7601
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">12517
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7128
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -6507,80 +6329,77 @@
 </t>
         </is>
       </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
+      <c r="J42" s="3" t="n">
+        <v/>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>403</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">0132
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1147
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">432
-5
+          <t xml:space="preserve">5435
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
@@ -6589,23 +6408,14 @@
           <t>1613</t>
         </is>
       </c>
-      <c r="X42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">883
-</t>
-        </is>
-      </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">589
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
+      <c r="X42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Y42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v/>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -6622,152 +6432,77 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66668446
-</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22422
-</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>40131</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1517
-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7128
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">717774
-82
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24127
-8
-242257
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1859957
-5
-13 2
-529
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">068
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42529
-21222
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
-</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222224
-</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2222
-</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t>1613</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">589
-</t>
-        </is>
-      </c>
-      <c r="Z43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">352
-</t>
-        </is>
+      <c r="C43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Y43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v/>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -6784,144 +6519,77 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57244
-</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2771
-28 1
-187
-215
-</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">277
-0
-2644
-</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">662
-</t>
-        </is>
+      <c r="C44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v/>
       </c>
       <c r="H44" s="3" t="n">
         <v/>
       </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
+      <c r="I44" s="3" t="n">
+        <v/>
       </c>
       <c r="J44" s="3" t="n">
         <v/>
       </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">271
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
+      <c r="K44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v/>
       </c>
       <c r="M44" s="3" t="n">
         <v/>
       </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-21
-</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">960
-</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2424622
-2224
-</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70
-</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="T44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21694
-</t>
-        </is>
-      </c>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">599
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">859
-</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
+      <c r="N44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v/>
       </c>
       <c r="Y44" s="3" t="n">
         <v/>
       </c>
-      <c r="Z44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">352
-</t>
-        </is>
+      <c r="Z44" s="3" t="n">
+        <v/>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -6940,59 +6608,53 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101979
-</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1097
-</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">418
-</t>
-        </is>
+          <t xml:space="preserve">19112
+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v/>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>7546</t>
+          <t xml:space="preserve">756
+</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">679
+          <t xml:space="preserve">1079
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">440
+          <t xml:space="preserve">1440
 </t>
         </is>
       </c>
@@ -7004,59 +6666,61 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">512
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
+          <t xml:space="preserve">3880
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1986
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">710
+</t>
+        </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42529
-21222
+          <t xml:space="preserve">1660
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">547
+          <t xml:space="preserve">2169
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222224
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">8314
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">1683
+</t>
         </is>
       </c>
       <c r="X45" s="3" t="n">
@@ -7064,12 +6728,15 @@
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">82630
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3318
+</t>
+        </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -7086,11 +6753,8 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">478
-</t>
-        </is>
+      <c r="C46" s="3" t="n">
+        <v/>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
@@ -7100,25 +6764,25 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">1125
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">11694
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">6197
 </t>
         </is>
       </c>
@@ -7134,28 +6798,24 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
+      <c r="K46" s="3" t="n">
+        <v/>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -7166,38 +6826,33 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">060
 </t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">1297
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21694
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197 1
-</t>
-        </is>
+          <t xml:space="preserve">122615
+</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v/>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
@@ -7207,20 +6862,24 @@
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="Z46" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16801
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">819
+</t>
+        </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_pre_QA_QC.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3912
+          <t xml:space="preserve">3012 1
 </t>
         </is>
       </c>
@@ -703,13 +703,13 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11817
+          <t xml:space="preserve">1817
 </t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -739,13 +739,13 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
@@ -757,31 +757,31 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">2168
 </t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11141
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5425
+          <t xml:space="preserve">425
 </t>
         </is>
       </c>
@@ -793,19 +793,20 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222191
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>411</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -816,7 +817,8 @@
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">78
+</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -842,55 +844,63 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>445</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>411</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2154
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
-</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1295
+</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1194
+</t>
+        </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
@@ -900,12 +910,15 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1908
-</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
@@ -915,12 +928,13 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t xml:space="preserve">1806
+</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -930,34 +944,39 @@
 </t>
         </is>
       </c>
-      <c r="U5" s="3" t="n">
-        <v/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11895
+          <t xml:space="preserve">11995
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">183
+</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805
+          <t xml:space="preserve">805
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">665
 </t>
         </is>
       </c>
@@ -984,7 +1003,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -996,54 +1015,61 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
+          <t xml:space="preserve">1849
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>05</t>
+          <t xml:space="preserve">150
+</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">695
+</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">11011
+</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14110
+          <t xml:space="preserve">02110
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1131
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -1055,17 +1081,21 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">11584
+</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1141
+</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
@@ -1073,34 +1103,39 @@
 </t>
         </is>
       </c>
-      <c r="U6" s="3" t="n">
-        <v/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17158
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t xml:space="preserve">183
+</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1950
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">009
 </t>
         </is>
       </c>
@@ -1121,36 +1156,38 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12758
+          <t xml:space="preserve">2758
 </t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2019
 </t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">228595
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t xml:space="preserve">11129
+</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -1161,58 +1198,62 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">132
+</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">050
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>113</t>
+          <t xml:space="preserve">21193
+</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>433</t>
+          <t xml:space="preserve">0775
+</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1223,33 +1264,37 @@
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">1189
+</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>468</t>
+          <t xml:space="preserve">168
+</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t xml:space="preserve">810
+</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -1270,24 +1315,26 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3912
+          <t xml:space="preserve">2912
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>261</t>
+          <t xml:space="preserve">0263
+</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">01095
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1298,104 +1345,114 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t xml:space="preserve">35
+</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>408</t>
+          <t xml:space="preserve">108
+</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>4244</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">11906
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17180
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">102175
+</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">1189
+</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1760
+          <t xml:space="preserve">760
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1173
+          <t xml:space="preserve">1973
 </t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">870
+</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -1422,18 +1479,19 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>128491</t>
+          <t xml:space="preserve">1289
+</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
+          <t xml:space="preserve">554
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
+          <t xml:space="preserve">9119
 </t>
         </is>
       </c>
@@ -1445,53 +1503,55 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17026
+          <t xml:space="preserve">606
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t xml:space="preserve">99
+</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
+          <t xml:space="preserve">567
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t xml:space="preserve">552
+</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">551
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14848
+          <t xml:space="preserve">4848
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">026
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -1503,49 +1563,49 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1859
+          <t xml:space="preserve">853
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1885
+          <t xml:space="preserve">8853
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3805
+          <t xml:space="preserve">95015
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12333
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
+          <t xml:space="preserve">9117
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141545
+          <t xml:space="preserve">94145
 </t>
         </is>
       </c>
@@ -1572,7 +1632,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3499
+          <t xml:space="preserve">8499
 </t>
         </is>
       </c>
@@ -1584,66 +1644,73 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107974
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1113
+</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1110
 </t>
         </is>
       </c>
-      <c r="F10" s="3" t="n">
-        <v/>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12114
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1113
-</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11110
-</t>
-        </is>
-      </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t xml:space="preserve">2130
+</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1968
+          <t xml:space="preserve">968
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1015
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
@@ -1661,19 +1728,19 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1127
+          <t xml:space="preserve">1177
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141671
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">7 2
 </t>
         </is>
       </c>
@@ -1685,25 +1752,25 @@
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1829
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1510
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -1724,7 +1791,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15093
+          <t xml:space="preserve">9093
 </t>
         </is>
       </c>
@@ -1734,12 +1801,15 @@
 </t>
         </is>
       </c>
-      <c r="E11" s="3" t="n">
-        <v/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10479
+</t>
+        </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">2190
 </t>
         </is>
       </c>
@@ -1751,45 +1821,61 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">67
+</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1847
+</t>
+        </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64
+</t>
+        </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">119 0
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">518
+</t>
+        </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1042
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12263
+          <t xml:space="preserve">1665
 </t>
         </is>
       </c>
@@ -1801,12 +1887,14 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>401</t>
+          <t xml:space="preserve">8620
+</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -1817,18 +1905,20 @@
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2221
+          <t xml:space="preserve">1221
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">1176
+</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">116
+</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -1839,7 +1929,7 @@
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -1860,13 +1950,13 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13067
+          <t xml:space="preserve">5067
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -1878,48 +1968,49 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01450
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">2094
 </t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">2197
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -1937,19 +2028,20 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">155
+</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
@@ -1960,13 +2052,14 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">370
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">2046
+</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
@@ -1977,23 +2070,25 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">119
+</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t xml:space="preserve">197
+</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10920
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -2014,58 +2109,73 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13579
-</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">35149
+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11112
+</t>
+        </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11813
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">75
+</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t xml:space="preserve">23
+</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">996
+</t>
+        </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1836
+          <t xml:space="preserve">1136
 </t>
         </is>
       </c>
@@ -2077,33 +2187,37 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1097
+</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11809
+</t>
+        </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">173
+</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">864
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -2115,25 +2229,25 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">268164
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1840
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">936
 </t>
         </is>
       </c>
@@ -2154,65 +2268,73 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2270
+          <t xml:space="preserve">2210
 </t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>238</t>
+          <t xml:space="preserve">255
+</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01532
+          <t xml:space="preserve">030
 </t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11813
+          <t xml:space="preserve">11853
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+</t>
+        </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2182
-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">283
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111820
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t xml:space="preserve">1180
+</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -2224,62 +2346,67 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1069
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11266
-</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">195
+</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t xml:space="preserve">1160
+</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1950
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818110
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -2300,31 +2427,31 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16310
+          <t xml:space="preserve">16380
 </t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101108
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111815
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -2342,7 +2469,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -2354,19 +2481,19 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">1574
 </t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1213
+          <t xml:space="preserve">27113
 </t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -2378,51 +2505,56 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1012
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2255
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">11726
+</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="T15" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1579
+</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1680
+</t>
+        </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11165
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t xml:space="preserve">1694
+</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
@@ -2433,7 +2565,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -2460,25 +2592,25 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">12980
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2568
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
+          <t xml:space="preserve">9 5
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">792
+          <t xml:space="preserve">712
 </t>
         </is>
       </c>
@@ -2496,7 +2628,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">518
 </t>
         </is>
       </c>
@@ -2508,13 +2640,14 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">591
+          <t xml:space="preserve">5917
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>582</t>
+          <t xml:space="preserve">582
+</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2525,36 +2658,37 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4398
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111910
+          <t xml:space="preserve">171190
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">822
+</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7211
+          <t xml:space="preserve">777
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3101
+          <t xml:space="preserve">3108
 </t>
         </is>
       </c>
@@ -2566,31 +2700,32 @@
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9212
+          <t xml:space="preserve">956
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8019
+          <t xml:space="preserve">8017
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1822
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13640
+          <t xml:space="preserve">23698
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t>334</t>
+          <t xml:space="preserve">3939
+</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2610,7 +2745,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2459
+          <t xml:space="preserve">4459
 </t>
         </is>
       </c>
@@ -2622,49 +2757,49 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">118
 </t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11815
-</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1145
-</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79
-</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1118
-</t>
-        </is>
-      </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">116
@@ -2673,19 +2808,19 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
+          <t xml:space="preserve">2136
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1978
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1074
+          <t xml:space="preserve">074
 </t>
         </is>
       </c>
@@ -2697,31 +2832,31 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">722
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11196
+          <t xml:space="preserve">21196
 </t>
         </is>
       </c>
@@ -2733,7 +2868,8 @@
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">1165
+</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -2744,7 +2880,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -2765,79 +2901,85 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14358
+          <t xml:space="preserve">4551
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>22444</t>
+          <t xml:space="preserve">109
+</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">11380
+</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">07
+</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">017
 </t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">1615
+</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">876
+          <t xml:space="preserve">846
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1610
+          <t xml:space="preserve">216105
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -2849,19 +2991,19 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1723
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11154
+          <t xml:space="preserve">21014
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14060
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -2879,24 +3021,24 @@
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t xml:space="preserve">1155
+</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137910
-</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -2917,7 +3059,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15311
+          <t xml:space="preserve">953111
 </t>
         </is>
       </c>
@@ -2929,54 +3071,61 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72
+</t>
+        </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">33
+</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12110
+          <t xml:space="preserve">2112
 </t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17110
+          <t xml:space="preserve">11110
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">13 0
 </t>
         </is>
       </c>
@@ -2988,34 +3137,38 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t xml:space="preserve">162
+</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">948
+</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">1072
+</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
@@ -3026,7 +3179,8 @@
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>212</t>
+          <t xml:space="preserve">1178
+</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
@@ -3037,7 +3191,8 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t xml:space="preserve">740
+</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -3063,7 +3218,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5922
+          <t xml:space="preserve">5422
 </t>
         </is>
       </c>
@@ -3075,66 +3230,75 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12084
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t xml:space="preserve">119
+</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17335
+          <t xml:space="preserve">1335
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">1020
+</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">11112
+</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188181
-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">82212
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108110
+</t>
+        </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">982
+</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
@@ -3142,50 +3306,59 @@
 </t>
         </is>
       </c>
-      <c r="R20" s="3" t="n">
-        <v/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11513
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405
+          <t xml:space="preserve">405
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>924</t>
+          <t xml:space="preserve">224
+</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>184</t>
+          <t xml:space="preserve">1895
+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122982
+          <t xml:space="preserve">1299
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="Z20" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">7210
+</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -3210,61 +3383,69 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">1298
+</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t xml:space="preserve">187
+</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>421</t>
+          <t xml:space="preserve">1109
+</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1130
+</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1549
+</t>
+        </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
@@ -3274,40 +3455,43 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>224</t>
+          <t xml:space="preserve">256
+</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">182
+</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19310
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t xml:space="preserve">162
+</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -3325,13 +3509,13 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -3352,7 +3536,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14290
+          <t xml:space="preserve">1948288
 </t>
         </is>
       </c>
@@ -3362,38 +3546,45 @@
 </t>
         </is>
       </c>
-      <c r="E22" s="3" t="n">
-        <v/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
+          <t xml:space="preserve">1987
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t xml:space="preserve">1139
+</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">859
+</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1080
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -3405,59 +3596,61 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">9920
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11949
+          <t xml:space="preserve">0494
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>4434544</t>
+          <t xml:space="preserve">495
+</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>448</t>
+          <t xml:space="preserve">148
+</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1225
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -3469,19 +3662,19 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20139
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">505
+          <t xml:space="preserve">5059
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">11997
 </t>
         </is>
       </c>
@@ -3502,30 +3695,31 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232031
+          <t xml:space="preserve">123208
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1321
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t xml:space="preserve">2015
+</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">944
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7509
+          <t xml:space="preserve">757
 </t>
         </is>
       </c>
@@ -3537,98 +3731,109 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t xml:space="preserve">208
+</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1013
+          <t xml:space="preserve">059
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">618
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7115
+</t>
+        </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24930
-</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2930
+</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11289
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">781
+          <t xml:space="preserve">7817
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2357
+          <t xml:space="preserve">23517
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1885
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11067
+          <t xml:space="preserve">1067
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1855
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>263</t>
+          <t xml:space="preserve">862
+</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13415
+          <t xml:space="preserve">3415
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1410
+          <t xml:space="preserve">5410
 </t>
         </is>
       </c>
@@ -3661,25 +3866,25 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
+          <t xml:space="preserve">1 5 1
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -3691,12 +3896,15 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">761
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 8
+</t>
+        </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -3706,12 +3914,14 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
@@ -3721,7 +3931,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">034
 </t>
         </is>
       </c>
@@ -3733,37 +3943,38 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">1 29 6
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12479
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11975
+          <t xml:space="preserve">11777
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">913
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>411</t>
+          <t xml:space="preserve">177
+</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
@@ -3774,13 +3985,14 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1689
+          <t xml:space="preserve">1683
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t xml:space="preserve">82
+</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3800,113 +4012,132 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14889
+          <t xml:space="preserve">428 9
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
-</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1279
+</t>
+        </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v/>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v/>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v/>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1160
+</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11079
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1054
+</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t xml:space="preserve">241
+</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">10
+</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5493
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11518
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">01169
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">11 68
 </t>
         </is>
       </c>
@@ -3918,7 +4149,7 @@
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">656
 </t>
         </is>
       </c>
@@ -3939,13 +4170,13 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13499
+          <t xml:space="preserve">3499
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -3957,7 +4188,8 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">170
+</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -3968,48 +4200,57 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2194
+</t>
+        </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1102
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">981
+</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
@@ -4019,18 +4260,19 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>45474</t>
+          <t xml:space="preserve">157
+</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1635
+          <t xml:space="preserve">635
 </t>
         </is>
       </c>
@@ -4060,12 +4302,13 @@
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t xml:space="preserve">1940
+</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">2118
 </t>
         </is>
       </c>
@@ -4092,26 +4335,33 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t xml:space="preserve">125717
+</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
-</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">0117
+</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1181
+</t>
+        </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111440
-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">824
+</t>
+        </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
@@ -4121,60 +4371,66 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>424</t>
+          <t xml:space="preserve">1124
+</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">080
+</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11618
+          <t xml:space="preserve">116181
 </t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1860
+          <t xml:space="preserve">560
 </t>
         </is>
       </c>
@@ -4186,31 +4442,32 @@
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11875
+          <t xml:space="preserve">1158595
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">9130
 </t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4230,136 +4487,146 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151395
+          <t xml:space="preserve">3133
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11115
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">193
+</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11545
+          <t xml:space="preserve">11509
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t xml:space="preserve">55
+</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11133
+          <t xml:space="preserve">1133
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1680
+          <t xml:space="preserve">680
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="W28" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X28" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">16454
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2110
+</t>
+        </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">18910
 </t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">118
+</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4385,102 +4652,111 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t xml:space="preserve">0107
+</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">1195
+</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t xml:space="preserve">1181
+</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">72
+</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t xml:space="preserve">38
+</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">6252
 </t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">11097
 </t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09105
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11224
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">969
+          <t xml:space="preserve">1960
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2270
+          <t xml:space="preserve">12170
 </t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11817
+          <t xml:space="preserve">15171
 </t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">478
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">578
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
@@ -4488,21 +4764,27 @@
 </t>
         </is>
       </c>
-      <c r="W29" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X29" s="3" t="n">
-        <v/>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1127
+</t>
+        </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600
+          <t xml:space="preserve">600
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
@@ -4523,7 +4805,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228481
+          <t xml:space="preserve">22 848 3
 </t>
         </is>
       </c>
@@ -4535,13 +4817,13 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1529
+          <t xml:space="preserve">527
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">917
 </t>
         </is>
       </c>
@@ -4553,7 +4835,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">2160
 </t>
         </is>
       </c>
@@ -4565,7 +4847,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11195
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
@@ -4577,47 +4859,49 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">522
+          <t xml:space="preserve">512
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">561
+          <t xml:space="preserve">567
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">65
+</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14890
+          <t xml:space="preserve">94890
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
+          <t xml:space="preserve">11132
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">867
+          <t xml:space="preserve">8517
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1844
+          <t xml:space="preserve">8447
 </t>
         </is>
       </c>
@@ -4629,7 +4913,7 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">559
+          <t xml:space="preserve">354
 </t>
         </is>
       </c>
@@ -4641,7 +4925,7 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
@@ -4653,7 +4937,7 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13650
+          <t xml:space="preserve">3650
 </t>
         </is>
       </c>
@@ -4680,7 +4964,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14520
+          <t xml:space="preserve">15320
 </t>
         </is>
       </c>
@@ -4692,30 +4976,33 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1584
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">721
-</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">724
+</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -4723,8 +5010,11 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="n">
-        <v/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
@@ -4734,12 +5024,15 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14128
+</t>
+        </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
@@ -4749,7 +5042,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8404
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
@@ -4761,7 +5054,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21793
+          <t xml:space="preserve">1125
 </t>
         </is>
       </c>
@@ -4773,19 +5066,19 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">630
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">211 1
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19 9
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -4803,7 +5096,7 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730 0
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -4830,31 +5123,31 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5208
+          <t xml:space="preserve">05280
 </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">2289
 </t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11102
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22177
+          <t xml:space="preserve">1177
 </t>
         </is>
       </c>
@@ -4866,101 +5159,111 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110905
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1033</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">0101
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1625
-</t>
-        </is>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20214
+          <t xml:space="preserve">0214
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
+          <t xml:space="preserve">20179
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">709
-</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -4985,59 +5288,73 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">2462
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>288</t>
+          <t xml:space="preserve">1128
+</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121114
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1959
+</t>
+        </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">815
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1186
+</t>
+        </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">9808
 </t>
         </is>
       </c>
@@ -5049,12 +5366,14 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t xml:space="preserve">12035
+</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>438</t>
+          <t xml:space="preserve">178
+</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -5065,35 +5384,43 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">799
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">50
+</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1199
+</t>
+        </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -5114,7 +5441,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3291
+          <t xml:space="preserve">3299
 </t>
         </is>
       </c>
@@ -5126,7 +5453,8 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>443</t>
+          <t xml:space="preserve">1149
+</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -5137,29 +5465,31 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">215
+</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -5171,58 +5501,61 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1078
+</t>
+        </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">0990
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11818
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">726
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112871
+          <t xml:space="preserve">1877
 </t>
         </is>
       </c>
@@ -5232,18 +5565,21 @@
 </t>
         </is>
       </c>
-      <c r="X34" s="3" t="n">
-        <v/>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1810
+</t>
+        </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8930
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5264,30 +5600,31 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15067
+          <t xml:space="preserve">50567
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">2568
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>231</t>
+          <t xml:space="preserve">1128
+</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21540
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -5299,17 +5636,19 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t xml:space="preserve">36
+</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>515</t>
+          <t xml:space="preserve">211
+</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5321,30 +5660,37 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1848
+</t>
+        </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>490</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">18910
+</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">2388
 </t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11476
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -5356,13 +5702,13 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5720
+          <t xml:space="preserve">2520
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">2128
 </t>
         </is>
       </c>
@@ -5374,19 +5720,20 @@
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5162
+          <t xml:space="preserve">1679
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141168
+          <t xml:space="preserve">4168
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>685</t>
+          <t xml:space="preserve">1685
+</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
@@ -5418,19 +5765,19 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2563
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">009
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1813
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -5460,24 +5807,27 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11016
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11105
-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1126
+</t>
+        </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
@@ -5487,36 +5837,37 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>255</t>
+          <t xml:space="preserve">255
+</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1711
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">1658
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6850
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
@@ -5528,27 +5879,24 @@
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="Z36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11108
-</t>
-        </is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v/>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -5567,41 +5915,43 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22404
+          <t xml:space="preserve">22909
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>184</t>
+          <t xml:space="preserve">1285
+</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1609
+          <t xml:space="preserve">609
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9917
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">6566
+</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1460
+          <t xml:space="preserve">460
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1161
+          <t xml:space="preserve">1679
 </t>
         </is>
       </c>
@@ -5613,42 +5963,49 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650
-</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">630
+</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">645
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">746
+</t>
+        </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24920
+          <t xml:space="preserve">4920
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">8119
 </t>
         </is>
       </c>
@@ -5660,31 +6017,31 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2169
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
+          <t xml:space="preserve">5545
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11009
+          <t xml:space="preserve">1009
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1831
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">898
 </t>
         </is>
       </c>
@@ -5696,7 +6053,7 @@
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3946
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
@@ -5717,7 +6074,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24481
+          <t xml:space="preserve">4489
 </t>
         </is>
       </c>
@@ -5729,92 +6086,103 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11122
+          <t xml:space="preserve">1122
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1135
+</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9201
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1130
+</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">028
+</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9849
+</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12176
+</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">835
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1189
 </t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11351
-</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5921
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1130
-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1128
-</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="n">
-        <v/>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">989
-</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">633
-</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t>4243</t>
-        </is>
-      </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">202
@@ -5823,7 +6191,7 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">101166
 </t>
         </is>
       </c>
@@ -5835,13 +6203,13 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -5862,7 +6230,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35999
+          <t xml:space="preserve">53729
 </t>
         </is>
       </c>
@@ -5874,55 +6242,70 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">711180
+          <t xml:space="preserve">2290
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1189
+</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
       </c>
       <c r="H39" s="3" t="n">
         <v/>
       </c>
-      <c r="I39" s="3" t="n">
-        <v/>
-      </c>
-      <c r="J39" s="3" t="n">
-        <v/>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70
+</t>
+        </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v/>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1127
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1823
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1192
+</t>
+        </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19808
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">049
 </t>
         </is>
       </c>
@@ -5934,18 +6317,19 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">0180
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">102
+</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17200
+          <t xml:space="preserve">581469
 </t>
         </is>
       </c>
@@ -5957,18 +6341,19 @@
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t>212</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181517
+          <t xml:space="preserve">81575
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21196
+          <t xml:space="preserve">1123
 </t>
         </is>
       </c>
@@ -5980,7 +6365,8 @@
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t xml:space="preserve">1416
+</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6000,19 +6386,19 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351
+          <t xml:space="preserve">525
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -6024,19 +6410,19 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">5129
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -6045,40 +6431,43 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -6090,40 +6479,43 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">699
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0168
+          <t xml:space="preserve">11813
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21993
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
@@ -6150,37 +6542,37 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2454512
+          <t xml:space="preserve">4582
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112813
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1510
+          <t xml:space="preserve">1519
 </t>
         </is>
       </c>
@@ -6190,37 +6582,46 @@
 </t>
         </is>
       </c>
-      <c r="J41" s="3" t="n">
-        <v/>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 185
+          <t xml:space="preserve">887
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">8 6
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
@@ -6230,38 +6631,45 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57179
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72166
-</t>
-        </is>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42135
+</t>
+        </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1127
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
@@ -6271,7 +6679,7 @@
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
+          <t xml:space="preserve">11120
 </t>
         </is>
       </c>
@@ -6292,16 +6700,19 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5244
-</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">52544
+</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
+</t>
+        </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7601
+          <t xml:space="preserve">8811
 </t>
         </is>
       </c>
@@ -6313,28 +6724,31 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12517
+          <t xml:space="preserve">11517
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6346,19 +6760,20 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0132
+          <t xml:space="preserve">1133
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>160</t>
+          <t xml:space="preserve">960
+</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -6375,41 +6790,45 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">11487
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5435
+          <t xml:space="preserve">1532
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">020
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>1613</t>
-        </is>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
       </c>
       <c r="Y42" s="3" t="n">
         <v/>
@@ -6432,8 +6851,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n">
-        <v/>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="D43" s="3" t="n">
         <v/>
@@ -6519,8 +6941,11 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n">
-        <v/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
       </c>
       <c r="D44" s="3" t="n">
         <v/>
@@ -6612,11 +7037,17 @@
 </t>
         </is>
       </c>
-      <c r="D45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v/>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1097
+</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">418
+</t>
+        </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -6626,47 +7057,49 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1079
+          <t xml:space="preserve">079
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t xml:space="preserve">1194
+</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1440
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">2129
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">512
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
@@ -6678,12 +7111,13 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">223
+</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1986
+          <t xml:space="preserve">986
 </t>
         </is>
       </c>
@@ -6695,7 +7129,7 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1660
+          <t xml:space="preserve">660
 </t>
         </is>
       </c>
@@ -6707,19 +7141,19 @@
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314
+          <t xml:space="preserve">8519
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1683
+          <t xml:space="preserve">673
 </t>
         </is>
       </c>
@@ -6728,13 +7162,13 @@
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82630
+          <t xml:space="preserve">12630
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3318
+          <t xml:space="preserve">3319
 </t>
         </is>
       </c>
@@ -6753,8 +7187,11 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n">
-        <v/>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54178
+</t>
+        </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
@@ -6764,37 +7201,37 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1125
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11694
+          <t xml:space="preserve">1694
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6197
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
+          <t xml:space="preserve">1524
 </t>
         </is>
       </c>
@@ -6803,56 +7240,63 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">1411
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">128
+</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">1970
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">060
+          <t xml:space="preserve">064
 </t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
+          <t xml:space="preserve">2 47 1
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122615
-</t>
-        </is>
-      </c>
-      <c r="T46" s="3" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6547
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14 7
+</t>
+        </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
@@ -6871,7 +7315,7 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16801
+          <t xml:space="preserve">18608
 </t>
         </is>
       </c>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_pre_QA_QC.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3012 1
+          <t xml:space="preserve">3012
 </t>
         </is>
       </c>
@@ -709,7 +709,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -751,46 +751,46 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">9280
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1141
+</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4625
+</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1191
 </t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">425
-</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">221
@@ -817,7 +817,7 @@
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">738
 </t>
         </is>
       </c>
@@ -862,7 +862,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1594
 </t>
         </is>
       </c>
@@ -892,13 +892,13 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1295
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">181494
 </t>
         </is>
       </c>
@@ -916,7 +916,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -928,7 +928,7 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1806
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -944,21 +944,18 @@
 </t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
+      <c r="U5" s="3" t="n">
+        <v/>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11995
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -976,7 +973,7 @@
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">665
+          <t xml:space="preserve">4695
 </t>
         </is>
       </c>
@@ -1015,7 +1012,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849
+          <t xml:space="preserve">1894
 </t>
         </is>
       </c>
@@ -1027,7 +1024,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -1045,19 +1042,19 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">695
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11011
+          <t xml:space="preserve">1011
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -1081,13 +1078,13 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11584
+          <t xml:space="preserve">1154
 </t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -1105,7 +1102,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -1117,13 +1114,13 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -1135,7 +1132,7 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">009
+          <t xml:space="preserve">029
 </t>
         </is>
       </c>
@@ -1162,13 +1159,13 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228595
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -1186,7 +1183,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11129
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
@@ -1198,7 +1195,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -1228,7 +1225,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
@@ -1240,46 +1237,46 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21193
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0177
+</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0775
-</t>
-        </is>
-      </c>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">790
-</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1189
-</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">179
@@ -1294,7 +1291,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -1315,19 +1312,19 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2912
+          <t xml:space="preserve">3912
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0263
+          <t xml:space="preserve">2673
 </t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01095
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -1363,7 +1360,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1375,13 +1372,13 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11906
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1393,19 +1390,19 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102175
+          <t xml:space="preserve">227194
 </t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -1434,7 +1431,7 @@
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1973
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -1473,8 +1470,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17497
-</t>
+          <t>439274</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1485,13 +1481,13 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">554
+          <t xml:space="preserve">550
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9119
+          <t xml:space="preserve">919
 </t>
         </is>
       </c>
@@ -1503,32 +1499,31 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">606
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">979
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1539,13 +1534,13 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">551
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4848
+          <t xml:space="preserve">6848
 </t>
         </is>
       </c>
@@ -1569,13 +1564,13 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8853
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95015
+          <t xml:space="preserve">38015
 </t>
         </is>
       </c>
@@ -1587,19 +1582,19 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9117
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
@@ -1611,7 +1606,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1632,7 +1627,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8499
+          <t xml:space="preserve">3499
 </t>
         </is>
       </c>
@@ -1644,112 +1639,109 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24181
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1113
+</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1110
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2130
+</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">968
+</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203
+</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1177
+</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 24
+</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107974
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1113
-</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1110
-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2130
-</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">968
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05
-</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1177
-</t>
-        </is>
-      </c>
-      <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">267
-</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7 2
-</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1170
@@ -1770,7 +1762,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -1791,7 +1783,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9093
+          <t xml:space="preserve">5093
 </t>
         </is>
       </c>
@@ -1809,7 +1801,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2190
+          <t xml:space="preserve">2110
 </t>
         </is>
       </c>
@@ -1827,7 +1819,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1847
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
@@ -1845,37 +1837,37 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119 0
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">518
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1665
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
@@ -1887,13 +1879,13 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8620
+          <t xml:space="preserve">5120
 </t>
         </is>
       </c>
@@ -1905,7 +1897,7 @@
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -1917,7 +1909,7 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -1950,13 +1942,13 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5067
+          <t xml:space="preserve">5061
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">2059
 </t>
         </is>
       </c>
@@ -1974,43 +1966,43 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2094
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2197
+          <t xml:space="preserve">11917
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">8221
 </t>
         </is>
       </c>
@@ -2022,7 +2014,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1950
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
@@ -2034,7 +2026,7 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -2058,7 +2050,7 @@
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2046
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -2070,25 +2062,25 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
+          <t xml:space="preserve">520
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -2109,7 +2101,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35149
+          <t xml:space="preserve">3579
 </t>
         </is>
       </c>
@@ -2121,19 +2113,19 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11112
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -2145,13 +2137,13 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -2163,19 +2155,19 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
+          <t xml:space="preserve">1236
 </t>
         </is>
       </c>
@@ -2187,13 +2179,13 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1097
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11809
+          <t xml:space="preserve">1809
 </t>
         </is>
       </c>
@@ -2211,7 +2203,7 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">864
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
@@ -2229,13 +2221,13 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268164
+          <t xml:space="preserve">17915
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
@@ -2247,7 +2239,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">936
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -2268,43 +2260,43 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2210
+          <t xml:space="preserve">2270
 </t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">030
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11853
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">1105
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2316,73 +2308,70 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1116
+</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2158
+</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1830
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1469
+</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1149
+</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">116
 </t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1180
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1141
-</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1166
-</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
+      <c r="T14" s="3" t="n">
+        <v/>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">1595
 </t>
         </is>
       </c>
@@ -2400,13 +2389,13 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">087
 </t>
         </is>
       </c>
@@ -2427,7 +2416,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16380
+          <t xml:space="preserve">6310
 </t>
         </is>
       </c>
@@ -2439,7 +2428,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -2481,19 +2470,19 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1574
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27113
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -2517,25 +2506,25 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11726
+          <t xml:space="preserve">1726
 </t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1579
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1680
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
@@ -2547,13 +2536,13 @@
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1694
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -2592,7 +2581,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12980
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
@@ -2604,7 +2593,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 5
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
@@ -2628,7 +2617,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">518
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -2640,7 +2629,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5917
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
@@ -2652,25 +2641,24 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">679
-</t>
+          <t>571</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">3990
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171190
+          <t xml:space="preserve">11110
 </t>
         </is>
       </c>
@@ -2682,25 +2670,25 @@
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">777
+          <t xml:space="preserve">787
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3108
+          <t xml:space="preserve">3109
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1609
+          <t xml:space="preserve">609
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">956
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -2718,13 +2706,13 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23698
+          <t xml:space="preserve">3690
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3939
+          <t xml:space="preserve">339
 </t>
         </is>
       </c>
@@ -2757,13 +2745,13 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1994
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -2775,7 +2763,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -2787,7 +2775,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">98718
 </t>
         </is>
       </c>
@@ -2808,7 +2796,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2136
+          <t xml:space="preserve">1136
 </t>
         </is>
       </c>
@@ -2820,7 +2808,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">074
+          <t xml:space="preserve">0 8
 </t>
         </is>
       </c>
@@ -2838,14 +2826,13 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">1155
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
-</t>
+          <t>420</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
@@ -2856,13 +2843,13 @@
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1161
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
@@ -2901,7 +2888,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4551
+          <t xml:space="preserve">4555
 </t>
         </is>
       </c>
@@ -2919,55 +2906,55 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11380
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615
+          <t xml:space="preserve">116666
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">846
+          <t xml:space="preserve">816
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216105
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
@@ -2991,25 +2978,25 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21014
+          <t xml:space="preserve">21104
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
@@ -3021,24 +3008,25 @@
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t xml:space="preserve">390
+</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
@@ -3059,7 +3047,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">953111
+          <t xml:space="preserve">5319
 </t>
         </is>
       </c>
@@ -3077,7 +3065,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3095,7 +3083,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -3107,19 +3095,19 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2112
+          <t xml:space="preserve">21112
 </t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11110
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
@@ -3137,13 +3125,13 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">0094
 </t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -3161,7 +3149,7 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -3179,13 +3167,13 @@
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -3230,13 +3218,13 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
+          <t xml:space="preserve">805
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
@@ -3260,37 +3248,37 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82212
+          <t xml:space="preserve">22110
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108110
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">982
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
@@ -3314,7 +3302,7 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -3338,19 +3326,19 @@
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1895
+          <t xml:space="preserve">1894
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1299
+          <t xml:space="preserve">12997
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7210
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
@@ -3389,7 +3377,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -3407,7 +3395,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
@@ -3419,7 +3407,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -3443,7 +3431,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1549
+          <t xml:space="preserve">0159
 </t>
         </is>
       </c>
@@ -3479,7 +3467,7 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
@@ -3515,7 +3503,7 @@
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -3536,7 +3524,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948288
+          <t xml:space="preserve">94890
 </t>
         </is>
       </c>
@@ -3548,43 +3536,43 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1987
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
@@ -3602,13 +3590,13 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9920
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -3620,7 +3608,7 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -3632,7 +3620,7 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0494
+          <t xml:space="preserve">1497
 </t>
         </is>
       </c>
@@ -3662,19 +3650,19 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">538
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5059
+          <t xml:space="preserve">505
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11997
+          <t xml:space="preserve">1397
 </t>
         </is>
       </c>
@@ -3695,19 +3683,19 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123208
+          <t xml:space="preserve">123203
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">1321
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2015
+          <t xml:space="preserve">2611
 </t>
         </is>
       </c>
@@ -3719,7 +3707,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">757
+          <t xml:space="preserve">754
 </t>
         </is>
       </c>
@@ -3743,7 +3731,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">059
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -3761,7 +3749,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7115
+          <t xml:space="preserve">715
 </t>
         </is>
       </c>
@@ -3785,19 +3773,18 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7817
+          <t xml:space="preserve">781
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23517
+          <t xml:space="preserve">2357
 </t>
         </is>
       </c>
@@ -3833,7 +3820,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5410
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
@@ -3854,7 +3841,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4841
+          <t xml:space="preserve">24641
 </t>
         </is>
       </c>
@@ -3872,13 +3859,13 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 5 1
+          <t xml:space="preserve">1571
 </t>
         </is>
       </c>
@@ -3890,21 +3877,18 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 8
-</t>
-        </is>
+          <t xml:space="preserve">7161
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v/>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -3914,13 +3898,13 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -3931,7 +3915,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">034
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -3949,19 +3933,19 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 29 6
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11777
+          <t xml:space="preserve">11771
 </t>
         </is>
       </c>
@@ -3973,7 +3957,7 @@
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -3985,7 +3969,7 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1683
+          <t xml:space="preserve">683
 </t>
         </is>
       </c>
@@ -4012,49 +3996,49 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">428 9
+          <t xml:space="preserve">14889
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">497
 </t>
         </is>
       </c>
@@ -4066,19 +4050,19 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1054
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
@@ -4096,19 +4080,19 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">2415
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1376
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4120,24 +4104,25 @@
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">01132
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>213</t>
+          <t xml:space="preserve">213
+</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01169
+          <t xml:space="preserve">82169
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 68
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
@@ -4149,7 +4134,7 @@
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -4200,31 +4185,31 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2194
+          <t xml:space="preserve">51094
 </t>
         </is>
       </c>
@@ -4236,19 +4221,19 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -4260,13 +4245,13 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
@@ -4290,25 +4275,25 @@
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1940
+          <t xml:space="preserve">1550
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
@@ -4335,78 +4320,79 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125717
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0117
+          <t xml:space="preserve">1171
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1240
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1124
+</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">140
 </t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">824
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1124
-</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>440</t>
-        </is>
-      </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
@@ -4418,7 +4404,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116181
+          <t xml:space="preserve">116182
 </t>
         </is>
       </c>
@@ -4430,7 +4416,7 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">560
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
@@ -4442,25 +4428,24 @@
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158595
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9130
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -4487,19 +4472,19 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3133
+          <t xml:space="preserve">5133
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
@@ -4511,7 +4496,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11509
+          <t xml:space="preserve">11565
 </t>
         </is>
       </c>
@@ -4523,25 +4508,25 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">19354
 </t>
         </is>
       </c>
@@ -4553,13 +4538,13 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -4571,13 +4556,13 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
@@ -4601,7 +4586,7 @@
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16454
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -4613,13 +4598,13 @@
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2110
+          <t xml:space="preserve">28170
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18910
+          <t xml:space="preserve">1910
 </t>
         </is>
       </c>
@@ -4646,19 +4631,19 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5233
+          <t xml:space="preserve">3233
 </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0107
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
@@ -4688,7 +4673,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6252
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -4700,7 +4685,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11097
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
@@ -4712,7 +4697,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -4724,31 +4709,31 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12170
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15171
+          <t xml:space="preserve">11817
 </t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
+          <t xml:space="preserve">478
 </t>
         </is>
       </c>
@@ -4766,13 +4751,13 @@
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1127
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -4784,7 +4769,7 @@
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
@@ -4805,7 +4790,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22 848 3
+          <t xml:space="preserve">22848
 </t>
         </is>
       </c>
@@ -4835,7 +4820,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -4859,7 +4844,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">512
+          <t xml:space="preserve">572
 </t>
         </is>
       </c>
@@ -4869,15 +4854,12 @@
 </t>
         </is>
       </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
+      <c r="N30" s="3" t="n">
+        <v/>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94890
+          <t xml:space="preserve">4890
 </t>
         </is>
       </c>
@@ -4889,19 +4871,19 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11132
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8517
+          <t xml:space="preserve">867
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8447
+          <t xml:space="preserve">844
 </t>
         </is>
       </c>
@@ -4913,7 +4895,7 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">354
+          <t xml:space="preserve">559
 </t>
         </is>
       </c>
@@ -4964,13 +4946,13 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15320
+          <t xml:space="preserve">4320
 </t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">26 2
 </t>
         </is>
       </c>
@@ -4994,7 +4976,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">724
+          <t xml:space="preserve">721
 </t>
         </is>
       </c>
@@ -5010,11 +4992,8 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
+      <c r="K31" s="3" t="n">
+        <v/>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
@@ -5024,13 +5003,13 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14128
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -5042,7 +5021,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -5054,7 +5033,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1125
+          <t xml:space="preserve">7193
 </t>
         </is>
       </c>
@@ -5066,25 +5045,25 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211 1
+          <t xml:space="preserve">111 1
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -5096,7 +5075,7 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">730
 </t>
         </is>
       </c>
@@ -5123,13 +5102,13 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05280
+          <t xml:space="preserve">52808
 </t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2289
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
@@ -5147,7 +5126,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1177
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
@@ -5159,13 +5138,13 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -5183,61 +5162,61 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0101
+          <t xml:space="preserve">2201
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0214
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -5249,19 +5228,19 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20179
+          <t xml:space="preserve">2179
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1700
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -5288,7 +5267,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2462
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -5300,91 +5279,91 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1289
+</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11114
+</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1116
-</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1959
-</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1186
-</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9808
-</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12035
-</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1189
-</t>
-        </is>
-      </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -5396,13 +5375,13 @@
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -5414,13 +5393,13 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -5453,7 +5432,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">1147
 </t>
         </is>
       </c>
@@ -5471,19 +5450,19 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">1497
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">715
 </t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5495,25 +5474,25 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1078
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0990
+          <t xml:space="preserve">9910
 </t>
         </is>
       </c>
@@ -5531,7 +5510,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -5549,37 +5528,36 @@
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1877
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">330
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -5600,118 +5578,118 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50567
+          <t xml:space="preserve">5067
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2568
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95
+</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1130
+</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1890
+</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">520
+</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1128
 </t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">95
-</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1130
-</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1848
-</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18910
-</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2388
-</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="S35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="T35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2520
-</t>
-        </is>
-      </c>
-      <c r="U35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2128
-</t>
-        </is>
-      </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">208
@@ -5720,19 +5698,19 @@
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1679
+          <t xml:space="preserve">1167
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4168
+          <t xml:space="preserve">8168
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1685
+          <t xml:space="preserve">6835
 </t>
         </is>
       </c>
@@ -5771,19 +5749,19 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">11054
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -5825,13 +5803,13 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -5855,13 +5833,13 @@
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1658
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">050
 </t>
         </is>
       </c>
@@ -5879,19 +5857,18 @@
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
-</t>
+          <t>446</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
@@ -5915,8 +5892,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22909
-</t>
+          <t>21404</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5939,7 +5915,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6566
+          <t xml:space="preserve">6726
 </t>
         </is>
       </c>
@@ -5951,7 +5927,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1679
+          <t xml:space="preserve">1417
 </t>
         </is>
       </c>
@@ -5969,19 +5945,19 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">630
+          <t xml:space="preserve">650
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">645
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">746
+          <t xml:space="preserve">742
 </t>
         </is>
       </c>
@@ -5993,19 +5969,18 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">1859
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8119
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
@@ -6017,13 +5992,13 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">2169
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5545
+          <t xml:space="preserve">545
 </t>
         </is>
       </c>
@@ -6035,13 +6010,13 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
+          <t xml:space="preserve">8371
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -6053,7 +6028,7 @@
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">394
 </t>
         </is>
       </c>
@@ -6074,7 +6049,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4489
+          <t xml:space="preserve">4481
 </t>
         </is>
       </c>
@@ -6086,7 +6061,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -6116,7 +6091,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9201
+          <t xml:space="preserve">901
 </t>
         </is>
       </c>
@@ -6131,25 +6106,25 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">028
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9849
+          <t xml:space="preserve">984
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">3 8
 </t>
         </is>
       </c>
@@ -6167,19 +6142,19 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12176
+          <t xml:space="preserve">11276
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
@@ -6191,7 +6166,7 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101166
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
@@ -6203,7 +6178,7 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">719
 </t>
         </is>
       </c>
@@ -6230,7 +6205,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53729
+          <t xml:space="preserve">5799
 </t>
         </is>
       </c>
@@ -6242,7 +6217,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2290
+          <t xml:space="preserve">2110
 </t>
         </is>
       </c>
@@ -6254,7 +6229,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -6263,7 +6238,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">051
 </t>
         </is>
       </c>
@@ -6287,13 +6262,13 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1823
+          <t xml:space="preserve">1025
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -6305,7 +6280,7 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">049
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
@@ -6317,19 +6292,18 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">581469
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
@@ -6347,7 +6321,7 @@
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81575
+          <t xml:space="preserve">8157
 </t>
         </is>
       </c>
@@ -6365,7 +6339,7 @@
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -6386,7 +6360,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">525
+          <t xml:space="preserve">355
 </t>
         </is>
       </c>
@@ -6398,7 +6372,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -6410,19 +6384,19 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5129
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
@@ -6461,13 +6435,13 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -6479,13 +6453,13 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">699
+          <t xml:space="preserve">695
 </t>
         </is>
       </c>
@@ -6503,7 +6477,7 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11813
+          <t xml:space="preserve">11815
 </t>
         </is>
       </c>
@@ -6515,13 +6489,13 @@
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -6542,21 +6516,18 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4582
+          <t xml:space="preserve">4512
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v/>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -6570,15 +6541,12 @@
 </t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1519
-</t>
-        </is>
+      <c r="H41" s="3" t="n">
+        <v/>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">3
 </t>
         </is>
       </c>
@@ -6596,7 +6564,7 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">887
+          <t xml:space="preserve">883
 </t>
         </is>
       </c>
@@ -6631,19 +6599,19 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42135
+          <t xml:space="preserve">4235
 </t>
         </is>
       </c>
@@ -6661,13 +6629,13 @@
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -6679,7 +6647,7 @@
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11120
+          <t xml:space="preserve">0198
 </t>
         </is>
       </c>
@@ -6700,7 +6668,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52544
+          <t xml:space="preserve">5294
 </t>
         </is>
       </c>
@@ -6712,7 +6680,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8811
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -6724,7 +6692,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11517
+          <t xml:space="preserve">113517
 </t>
         </is>
       </c>
@@ -6736,7 +6704,7 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
@@ -6754,19 +6722,19 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -6790,19 +6758,19 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">1876
 </t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11487
+          <t xml:space="preserve">2127
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1532
+          <t xml:space="preserve">435
 </t>
         </is>
       </c>
@@ -6814,19 +6782,19 @@
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">020
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -7039,13 +7007,13 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1097
+          <t xml:space="preserve">10917
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">618
 </t>
         </is>
       </c>
@@ -7057,19 +7025,19 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">079
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
@@ -7087,19 +7055,19 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">440
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2129
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
@@ -7111,7 +7079,7 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -7141,24 +7109,27 @@
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8519
+          <t xml:space="preserve">8319
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">673
-</t>
-        </is>
-      </c>
-      <c r="X45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">675
+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2008
+</t>
+        </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
@@ -7168,7 +7139,7 @@
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3319
+          <t xml:space="preserve">23318
 </t>
         </is>
       </c>
@@ -7189,7 +7160,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54178
+          <t xml:space="preserve">4178
 </t>
         </is>
       </c>
@@ -7231,7 +7202,7 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1524
+          <t xml:space="preserve">621
 </t>
         </is>
       </c>
@@ -7240,13 +7211,13 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1411
+          <t xml:space="preserve">1111819
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -7270,13 +7241,13 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 47 1
+          <t xml:space="preserve">2 47
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1886
 </t>
         </is>
       </c>
@@ -7288,15 +7259,12 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6547
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14 7
-</t>
-        </is>
+          <t xml:space="preserve">541
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v/>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
@@ -7306,16 +7274,19 @@
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18608
+          <t xml:space="preserve">18624
 </t>
         </is>
       </c>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_pre_QA_QC.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3012
+          <t xml:space="preserve">3912
 </t>
         </is>
       </c>
@@ -697,7 +697,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1815
 </t>
         </is>
       </c>
@@ -709,7 +709,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -727,13 +727,13 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -745,19 +745,19 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9280
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
@@ -775,13 +775,13 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4625
+          <t xml:space="preserve">425
 </t>
         </is>
       </c>
@@ -805,7 +805,7 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
@@ -817,7 +817,7 @@
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">738
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
@@ -862,13 +862,13 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1594
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
@@ -886,7 +886,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -898,7 +898,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181494
+          <t xml:space="preserve">11194
 </t>
         </is>
       </c>
@@ -922,7 +922,7 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -944,8 +944,11 @@
 </t>
         </is>
       </c>
-      <c r="U5" s="3" t="n">
-        <v/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -955,7 +958,7 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -973,7 +976,7 @@
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4695
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -1006,13 +1009,13 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">1079
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
@@ -1024,7 +1027,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -1042,19 +1045,19 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1011
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
@@ -1090,7 +1093,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1102,25 +1105,25 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1183,25 +1186,25 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -1213,49 +1216,49 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
+          <t xml:space="preserve">1237
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">050
+          <t xml:space="preserve">10150
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">022
 </t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0177
+          <t xml:space="preserve">971
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
@@ -1279,7 +1282,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
@@ -1291,7 +1294,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
@@ -1318,13 +1321,13 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2673
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -1342,7 +1345,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
@@ -1378,7 +1381,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
@@ -1390,30 +1393,31 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227194
+          <t xml:space="preserve">1274
 </t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">195
+</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
+          <t xml:space="preserve">1760
 </t>
         </is>
       </c>
@@ -1425,19 +1429,19 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1973
 </t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
@@ -1470,7 +1474,8 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>439274</t>
+          <t xml:space="preserve">17497
+</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1493,19 +1498,19 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">739
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1406
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">979
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -1517,38 +1522,34 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>567</t>
+          <t xml:space="preserve">567
+</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">552
+          <t xml:space="preserve">5512
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">551
-</t>
+          <t>7661</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6848
-</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
+          <t>4849</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v/>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
@@ -1558,19 +1559,19 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
+          <t xml:space="preserve">1853
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38015
+          <t xml:space="preserve">3805
 </t>
         </is>
       </c>
@@ -1588,7 +1589,7 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">849
 </t>
         </is>
       </c>
@@ -1600,7 +1601,7 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94145
+          <t xml:space="preserve">4145
 </t>
         </is>
       </c>
@@ -1627,7 +1628,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3499
+          <t xml:space="preserve">83499
 </t>
         </is>
       </c>
@@ -1669,7 +1670,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24181
+          <t xml:space="preserve">2094
 </t>
         </is>
       </c>
@@ -1678,13 +1679,13 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -1702,7 +1703,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
@@ -1714,25 +1715,25 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">11 77
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1177
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">769
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7 24
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -1744,7 +1745,7 @@
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -1760,11 +1761,8 @@
 </t>
         </is>
       </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
+      <c r="Z10" s="3" t="n">
+        <v/>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1789,25 +1787,25 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10479
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2110
+          <t xml:space="preserve">0190
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
@@ -1831,40 +1829,40 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">02
 </t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1263
@@ -1879,19 +1877,19 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5120
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
@@ -1903,19 +1901,19 @@
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1176
 </t>
         </is>
       </c>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
@@ -1942,13 +1940,13 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5061
+          <t xml:space="preserve">5087
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2059
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -1960,13 +1958,13 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1894
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
@@ -1978,13 +1976,13 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
@@ -1996,13 +1994,13 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11917
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8221
+          <t xml:space="preserve">2119
 </t>
         </is>
       </c>
@@ -2032,7 +2030,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">1155
 </t>
         </is>
       </c>
@@ -2062,19 +2060,19 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
@@ -2131,25 +2129,25 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">1994
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
@@ -2161,13 +2159,13 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">1136
 </t>
         </is>
       </c>
@@ -2185,7 +2183,7 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -2197,19 +2195,19 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
+          <t xml:space="preserve">1854
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -2221,13 +2219,13 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17915
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
@@ -2266,136 +2264,139 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1159
+</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1285
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">467
+</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1130
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">097
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1849
+</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1970
+</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1162
+</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1160
+</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">950
+</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283
-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1116
-</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2158
-</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1830
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1469
-</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1595
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1160
-</t>
-        </is>
-      </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">950
-</t>
-        </is>
-      </c>
-      <c r="Z14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">087
 </t>
         </is>
       </c>
@@ -2428,19 +2429,19 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">11815
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">1508
 </t>
         </is>
       </c>
@@ -2470,7 +2471,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">774
 </t>
         </is>
       </c>
@@ -2506,13 +2507,13 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1726
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1157
 </t>
         </is>
       </c>
@@ -2524,13 +2525,13 @@
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
@@ -2554,7 +2555,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -2573,11 +2574,8 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22271
-</t>
-        </is>
+      <c r="C16" s="3" t="n">
+        <v/>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
@@ -2587,7 +2585,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">568 1
 </t>
         </is>
       </c>
@@ -2611,7 +2609,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -2641,12 +2639,12 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>84</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3990
+          <t xml:space="preserve">4898
 </t>
         </is>
       </c>
@@ -2670,31 +2668,31 @@
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
+          <t xml:space="preserve">777
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3109
+          <t xml:space="preserve">3108
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">609
+          <t xml:space="preserve">6039
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">9582
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8017
+          <t xml:space="preserve">8019
 </t>
         </is>
       </c>
@@ -2706,14 +2704,13 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3690
+          <t xml:space="preserve">3640
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">339
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2745,7 +2742,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1994
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -2775,7 +2772,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98718
+          <t xml:space="preserve">974
 </t>
         </is>
       </c>
@@ -2790,13 +2787,13 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
+          <t xml:space="preserve">2136
 </t>
         </is>
       </c>
@@ -2808,7 +2805,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 8
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -2820,24 +2817,25 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>420</t>
+          <t xml:space="preserve">3620
+</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -2849,7 +2847,7 @@
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">1161
 </t>
         </is>
       </c>
@@ -2861,13 +2859,13 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">8728
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -2888,7 +2886,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4555
+          <t xml:space="preserve">8455
 </t>
         </is>
       </c>
@@ -2906,25 +2904,25 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1871
 </t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -2942,25 +2940,24 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116666
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -2978,19 +2975,19 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21104
+          <t xml:space="preserve">1154
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -3008,25 +3005,25 @@
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">1155
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -3047,13 +3044,13 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5319
+          <t xml:space="preserve">5311
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -3065,13 +3062,13 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -3083,8 +3080,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -3101,19 +3097,19 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13 0
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -3125,7 +3121,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0094
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -3149,7 +3145,7 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">485
 </t>
         </is>
       </c>
@@ -3185,7 +3181,7 @@
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -3218,7 +3214,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
+          <t xml:space="preserve">1009
 </t>
         </is>
       </c>
@@ -3242,19 +3238,19 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1335
+          <t xml:space="preserve">1333
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -3266,19 +3262,19 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22110
+          <t xml:space="preserve">22140
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -3302,7 +3298,7 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -3314,7 +3310,7 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">12224
 </t>
         </is>
       </c>
@@ -3326,13 +3322,13 @@
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12997
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
@@ -3344,7 +3340,7 @@
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
@@ -3377,13 +3373,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">1027
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3395,7 +3391,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -3407,7 +3403,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -3419,25 +3415,25 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">1131
 </t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0159
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
@@ -3467,13 +3463,13 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3491,7 +3487,7 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">2009
 </t>
         </is>
       </c>
@@ -3503,7 +3499,7 @@
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -3524,7 +3520,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94890
+          <t xml:space="preserve">9890
 </t>
         </is>
       </c>
@@ -3536,25 +3532,25 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">1269
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">087
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">835
 </t>
         </is>
       </c>
@@ -3566,19 +3562,19 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1123
 </t>
         </is>
       </c>
@@ -3590,7 +3586,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -3620,13 +3616,13 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1497
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
+          <t xml:space="preserve">1495
 </t>
         </is>
       </c>
@@ -3644,13 +3640,13 @@
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">538
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
@@ -3683,19 +3679,19 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123203
+          <t xml:space="preserve">23223
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1321
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2611
+          <t xml:space="preserve">501
 </t>
         </is>
       </c>
@@ -3707,7 +3703,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">754
+          <t xml:space="preserve">759
 </t>
         </is>
       </c>
@@ -3719,13 +3715,13 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -3743,7 +3739,7 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
@@ -3755,13 +3751,13 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930
+          <t xml:space="preserve">24930
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -3773,12 +3769,13 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t xml:space="preserve">850
+</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">781
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
@@ -3841,7 +3838,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24641
+          <t xml:space="preserve">4641
 </t>
         </is>
       </c>
@@ -3859,13 +3856,13 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1571
+          <t xml:space="preserve">1151
 </t>
         </is>
       </c>
@@ -3877,18 +3874,21 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7161
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">721
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -3898,13 +3898,14 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">119
+</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -3927,7 +3928,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
@@ -3939,13 +3940,13 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">479
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11771
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -3957,20 +3958,19 @@
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
-</t>
+          <t>583</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
@@ -3996,79 +3996,79 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14889
+          <t xml:space="preserve">4889
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">97
+</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1109
+</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1107
+</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">29
 </t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">497
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1107
-</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -4080,31 +4080,31 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2415
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1376
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">495
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01132
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82169
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
@@ -4185,13 +4185,13 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
@@ -4209,19 +4209,19 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51094
+          <t xml:space="preserve">1104
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -4281,13 +4281,13 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">14 2
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1550
+          <t xml:space="preserve">550
 </t>
         </is>
       </c>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
+          <t xml:space="preserve">1117
 </t>
         </is>
       </c>
@@ -4356,19 +4356,19 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -4380,37 +4380,37 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116182
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1173
 </t>
         </is>
       </c>
@@ -4434,7 +4434,8 @@
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t xml:space="preserve">167
+</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
@@ -4445,7 +4446,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">12130
 </t>
         </is>
       </c>
@@ -4484,7 +4485,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
@@ -4496,7 +4497,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11565
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
@@ -4508,7 +4509,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -4520,13 +4521,13 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19354
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -4538,7 +4539,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -4562,7 +4563,7 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -4586,7 +4587,7 @@
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -4598,7 +4599,7 @@
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28170
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
@@ -4631,7 +4632,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3233
+          <t xml:space="preserve">5233
 </t>
         </is>
       </c>
@@ -4643,7 +4644,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
@@ -4655,7 +4656,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4685,7 +4686,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -4697,7 +4698,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -4709,25 +4710,25 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11817
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -4757,19 +4758,19 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">1600
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -4790,19 +4791,19 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22848
+          <t xml:space="preserve">2284
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1312
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">527
+          <t xml:space="preserve">5271
 </t>
         </is>
       </c>
@@ -4820,25 +4821,25 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -4854,8 +4855,11 @@
 </t>
         </is>
       </c>
-      <c r="N30" s="3" t="n">
-        <v/>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">659
+</t>
+        </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
@@ -4871,8 +4875,7 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
-</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
@@ -4895,7 +4898,7 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">559
+          <t xml:space="preserve">354
 </t>
         </is>
       </c>
@@ -4946,38 +4949,37 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320
+          <t xml:space="preserve">4520
 </t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26 2
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">11019
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1584
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">721
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -4988,7 +4990,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
@@ -4997,7 +4999,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -5009,7 +5011,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -5021,7 +5023,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -5033,7 +5035,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7193
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
@@ -5045,25 +5047,25 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">630
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111 1
+          <t xml:space="preserve">11114
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
@@ -5075,13 +5077,13 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">730 0
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">1658
 </t>
         </is>
       </c>
@@ -5102,7 +5104,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52808
+          <t xml:space="preserve">5200
 </t>
         </is>
       </c>
@@ -5114,7 +5116,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -5132,19 +5134,19 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -5156,37 +5158,37 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2201
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">12646
 </t>
         </is>
       </c>
@@ -5198,21 +5200,18 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="U32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
+          <t xml:space="preserve">626
+</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v/>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
@@ -5228,19 +5227,16 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2179
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1700
-</t>
-        </is>
+          <t xml:space="preserve">1172
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="n">
+        <v/>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">1718
 </t>
         </is>
       </c>
@@ -5279,25 +5275,25 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11114
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5315,79 +5311,79 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1185
+</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203
+</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">799
+</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">199
 </t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="T33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">299
-</t>
-        </is>
-      </c>
-      <c r="U33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1194
-</t>
-        </is>
-      </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
@@ -5399,7 +5395,7 @@
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -5438,7 +5434,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
@@ -5450,19 +5446,19 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1497
+          <t xml:space="preserve">1147
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">715
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -5474,25 +5470,25 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">1078
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9910
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -5516,7 +5512,7 @@
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -5528,30 +5524,31 @@
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">1287
+</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
@@ -5632,13 +5629,13 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -5650,13 +5647,13 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">3990
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -5674,43 +5671,43 @@
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">370
+</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1208
+</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1167
+</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="T35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">520
-</t>
-        </is>
-      </c>
-      <c r="U35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1128
-</t>
-        </is>
-      </c>
-      <c r="V35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="W35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1167
-</t>
-        </is>
-      </c>
-      <c r="X35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8168
-</t>
-        </is>
-      </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6835
+          <t xml:space="preserve">683
 </t>
         </is>
       </c>
@@ -5749,13 +5746,13 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11054
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -5773,7 +5770,7 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -5785,13 +5782,13 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1086
 </t>
         </is>
       </c>
@@ -5803,49 +5800,49 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">2171
 </t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">050
+          <t xml:space="preserve">630
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -5857,23 +5854,27 @@
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>446</t>
+          <t xml:space="preserve">146
+</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">1033
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
-        </is>
-      </c>
-      <c r="Z36" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">550
+</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -5892,7 +5893,8 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>21404</t>
+          <t xml:space="preserve">22404
+</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5909,13 +5911,13 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">947
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6726
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
@@ -5927,7 +5929,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1417
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -5939,19 +5941,19 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">650
+          <t xml:space="preserve">630
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
@@ -5967,20 +5969,18 @@
 </t>
         </is>
       </c>
-      <c r="P37" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="P37" s="3" t="n">
+        <v/>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1859
+          <t xml:space="preserve">1155
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
@@ -6010,25 +6010,25 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8371
+          <t xml:space="preserve">831
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">847
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3595
+          <t xml:space="preserve">3593
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">394
+          <t xml:space="preserve">346
 </t>
         </is>
       </c>
@@ -6049,7 +6049,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4481
+          <t xml:space="preserve">448
 </t>
         </is>
       </c>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">5921
 </t>
         </is>
       </c>
@@ -6100,13 +6100,13 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -6118,13 +6118,13 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
+          <t xml:space="preserve">2989
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 8
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -6136,13 +6136,13 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11276
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">11289
 </t>
         </is>
       </c>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -6205,8 +6205,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5799
-</t>
+          <t>5799</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -6217,28 +6216,31 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2110
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1159
+</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">051
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -6256,19 +6258,19 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1127
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1025
+          <t xml:space="preserve">1125
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
@@ -6286,60 +6288,58 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="n">
+        <v/>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">455
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">19 0
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8157
+          <t xml:space="preserve">2517
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
+          <t xml:space="preserve">560
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">1760
 </t>
         </is>
       </c>
@@ -6360,13 +6360,13 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">355
+          <t xml:space="preserve">3359
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -6384,24 +6384,27 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
@@ -6411,13 +6414,13 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">1103
 </t>
         </is>
       </c>
@@ -6429,19 +6432,19 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">1960
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -6453,13 +6456,13 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">695
+          <t xml:space="preserve">1695
 </t>
         </is>
       </c>
@@ -6477,25 +6480,25 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11815
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1175
+</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">293
 </t>
         </is>
       </c>
-      <c r="Y40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
@@ -6522,27 +6525,33 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">12894
+</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1510
+</t>
+        </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
@@ -6564,30 +6573,31 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 6
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">111
+</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">049
 </t>
         </is>
       </c>
@@ -6599,19 +6609,19 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4235
+          <t xml:space="preserve">579
 </t>
         </is>
       </c>
@@ -6629,16 +6639,16 @@
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">11815
+</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">163
 </t>
         </is>
       </c>
-      <c r="X41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">580
@@ -6647,7 +6657,7 @@
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0198
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
@@ -6668,7 +6678,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5294
+          <t xml:space="preserve">5244
 </t>
         </is>
       </c>
@@ -6680,7 +6690,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -6692,7 +6702,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113517
+          <t xml:space="preserve">125 7
 </t>
         </is>
       </c>
@@ -6704,7 +6714,7 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -6722,13 +6732,13 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -6758,45 +6768,39 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1876
+          <t xml:space="preserve">1126
 </t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2127
+          <t xml:space="preserve">1151
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">435
+          <t xml:space="preserve">532
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
-</t>
-        </is>
-      </c>
-      <c r="W42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="X42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v/>
       </c>
       <c r="Y42" s="3" t="n">
         <v/>
@@ -7001,19 +7005,19 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19112
+          <t xml:space="preserve">19812
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10917
+          <t xml:space="preserve">1097
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -7025,19 +7029,19 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">1079
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -7049,7 +7053,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -7061,13 +7065,13 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
@@ -7079,7 +7083,7 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -7103,7 +7107,7 @@
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2169
+          <t xml:space="preserve">2164
 </t>
         </is>
       </c>
@@ -7121,25 +7125,25 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">675
+          <t xml:space="preserve">673
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12630
+          <t xml:space="preserve">2630
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23318
+          <t xml:space="preserve">357
 </t>
         </is>
       </c>
@@ -7160,7 +7164,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4178
+          <t xml:space="preserve">4778
 </t>
         </is>
       </c>
@@ -7178,13 +7182,13 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1694
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -7196,28 +7200,31 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">361
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">621
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">652
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111819
+          <t xml:space="preserve">01117
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -7241,19 +7248,19 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 47
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
@@ -7263,8 +7270,11 @@
 </t>
         </is>
       </c>
-      <c r="U46" s="3" t="n">
-        <v/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
@@ -7280,13 +7290,13 @@
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18624
+          <t xml:space="preserve">2657
 </t>
         </is>
       </c>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_pre_QA_QC.xlsx
@@ -679,146 +679,122 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3912
-</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1815
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
-</t>
+          <t>425</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>710</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -838,146 +814,122 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3824
-</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11194
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
-</t>
+          <t>805</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -997,146 +949,122 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3091
-</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1079
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">029
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1156,146 +1084,122 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2758
-</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">971
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
-</t>
+          <t>790</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1315,146 +1219,122 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3912
-</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1274
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1760
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1973
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1474,68 +1354,57 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17497
-</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
-</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>919</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>739</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406
-</t>
+          <t>406</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5512
-</t>
+          <t>552</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1553,62 +1422,52 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1015
-</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1853
-</t>
+          <t>853</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3805
-</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">849
-</t>
+          <t>849</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
-</t>
+          <t>911</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1628,50 +1487,42 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83499
-</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2094
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="K10" s="3" t="n">
@@ -1679,86 +1530,72 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
-</t>
+          <t>968</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 77
-</t>
+          <t>1 71</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">769
-</t>
+          <t>761</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
-</t>
+          <t>829</t>
         </is>
       </c>
       <c r="Z10" s="3" t="n">
@@ -1781,146 +1618,122 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5093
-</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
-</t>
+          <t>420</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1940,146 +1753,122 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5087
-</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">370
-</t>
+          <t>370</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>520</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2099,146 +1888,122 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3579
-</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1994
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1854
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2258,146 +2023,122 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2270
-</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">467
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">097
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2417,146 +2158,122 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11815
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1508
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">774
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
-</t>
+          <t>480</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
-</t>
+          <t>670</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2579,62 +2296,52 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
-</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568 1
-</t>
+          <t>568</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">712
-</t>
+          <t>712</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">395
-</t>
+          <t>395</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
-</t>
+          <t>398</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>591</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
-</t>
+          <t>582</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2644,68 +2351,57 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4898
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11110
-</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">777
-</t>
+          <t>777</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3108
-</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6039
-</t>
+          <t>609</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9582
-</t>
+          <t>982</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8019
-</t>
+          <t>807</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3640
-</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2730,50 +2426,42 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4459
-</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="K17" s="3" t="n">
@@ -2781,92 +2469,77 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
+          <t>978</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3620
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8728
-</t>
+          <t>728</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2886,62 +2559,52 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8455
-</t>
+          <t>455</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -2951,80 +2614,67 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>462</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3044,38 +2694,32 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5311
-</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -3085,104 +2729,87 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">485
-</t>
+          <t>485</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3202,146 +2829,122 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5422
-</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1333
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22140
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">405
-</t>
+          <t>405</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>710</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3361,146 +2964,122 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3824
-</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1027
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
-</t>
+          <t>510</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3520,146 +3099,122 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9890
-</t>
+          <t>090</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">087
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1495
-</t>
+          <t>495</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">505
-</t>
+          <t>505</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3679,146 +3234,122 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23223
-</t>
+          <t>23203</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
-</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">501
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">944
-</t>
+          <t>944</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">759
-</t>
+          <t>754</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">406
-</t>
+          <t>406</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
-</t>
+          <t>618</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">715
-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
-</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>781</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2357
-</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1067
-</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3415
-</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
-</t>
+          <t>410</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3838,134 +3369,112 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4641
-</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">721
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>986</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">479
-</t>
+          <t>471</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -3975,8 +3484,7 @@
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3996,146 +3504,122 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4889
-</t>
+          <t>4889</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
-</t>
+          <t>495</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
+          <t>660</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4155,146 +3639,122 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3499
-</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">635
-</t>
+          <t>635</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14 2
-</t>
+          <t>14 2</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4314,146 +3774,122 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3402
-</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1117
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12130
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4473,146 +3909,122 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5133
-</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">680
-</t>
+          <t>680</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4632,146 +4044,122 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5233
-</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
-</t>
+          <t>960</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">478
-</t>
+          <t>478</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600
-</t>
+          <t>600</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4791,86 +4179,72 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2284
-</t>
+          <t>2284</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5271
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>917</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">791
-</t>
+          <t>791</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
-</t>
+          <t>572</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
-</t>
+          <t>561</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">659
-</t>
+          <t>659</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
-</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -4880,56 +4254,47 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">867
-</t>
+          <t>867</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
-</t>
+          <t>844</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">354
-</t>
+          <t>554</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">995
-</t>
+          <t>995</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>819</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3650
-</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">350
-</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4949,32 +4314,27 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4520
-</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11019
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -4984,14 +4344,12 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K31" s="3" t="n">
@@ -4999,92 +4357,77 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
+          <t>978</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">630
-</t>
+          <t>630</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11114
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730 0
-</t>
+          <t>730 2</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1658
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5104,110 +4447,92 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200
-</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12646
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
-</t>
+          <t>622</t>
         </is>
       </c>
       <c r="U32" s="3" t="n">
@@ -5215,20 +4540,17 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="Y32" s="3" t="n">
@@ -5236,8 +4558,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -5257,146 +4578,122 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3491
-</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">799
-</t>
+          <t>799</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5416,146 +4713,122 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3299
-</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1078
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
-</t>
+          <t>720</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1287
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5575,146 +4848,122 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5067
-</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">370
-</t>
+          <t>570</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
-</t>
+          <t>685</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5734,146 +4983,122 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5355
-</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1086
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">630
-</t>
+          <t>450</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1033
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5893,80 +5118,67 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22404
-</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
-</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">609
-</t>
+          <t>609</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">947
-</t>
+          <t>947</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
-</t>
+          <t>676</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">460
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">630
-</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
-</t>
+          <t>642</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
-</t>
+          <t>742</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P37" s="3" t="n">
@@ -5974,62 +5186,52 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
-</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>894</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2169
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
-</t>
+          <t>545</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009
-</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
-</t>
+          <t>831</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">847
-</t>
+          <t>847</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3593
-</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">346
-</t>
+          <t>346</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -6049,143 +5251,122 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">448
-</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5921
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v/>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2989
-</t>
+          <t>984</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>633</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11289
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>719</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -6210,92 +5391,77 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="S39" s="3" t="n">
@@ -6303,44 +5469,37 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">455
-</t>
+          <t>453</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19 0
-</t>
+          <t>19 0</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2517
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">560
-</t>
+          <t>560</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1760
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6360,146 +5519,122 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3359
-</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
-</t>
+          <t>960</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1695
-</t>
+          <t>695</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6519,146 +5654,122 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4512
-</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12894
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1510
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">049
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">579
-</t>
+          <t>579</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11815
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6678,122 +5789,102 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5244
-</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125 7
-</t>
+          <t>15 7</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
-</t>
+          <t>960</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
-</t>
+          <t>433</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W42" s="3" t="n">
@@ -6825,8 +5916,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
@@ -6915,8 +6005,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
@@ -7005,146 +6094,122 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19812
-</t>
+          <t>19112</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1097
-</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
-</t>
+          <t>418</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">756
-</t>
+          <t>756</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1079
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">440
-</t>
+          <t>440</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
-</t>
+          <t>429</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3880
-</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>986</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>710</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
+          <t>660</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2164
-</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8319
-</t>
+          <t>854</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">673
-</t>
+          <t>673</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630
-</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">357
-</t>
+          <t>357</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -7164,146 +6229,122 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4778
-</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">652
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11111000</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01117
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">064
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">541
-</t>
+          <t>541</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2657
-</t>
+          <t>657</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_pre_QA_QC.xlsx
@@ -724,7 +724,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>93</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>172</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>73</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>883</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>1 71</t>
+          <t>2 71</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>268</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>660</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>204</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>197</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>320</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>114</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>861</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
@@ -2058,17 +2058,17 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>167</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>232</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>162</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>568 8</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>294</t>
         </is>
       </c>
       <c r="K17" s="3" t="n">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>09</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>199</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>090</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>129</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>992</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>165</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>114</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -3404,12 +3404,12 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>421</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>011</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -3534,12 +3534,12 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>280</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>14 2</t>
+          <t>14 22</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -4064,64 +4064,64 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
           <t>170</t>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>278</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>2284</t>
+          <t>22848</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>360</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>109</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>132</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>188</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>166</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>141</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>178</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>530</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>370</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>179</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>460</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="P37" s="3" t="n">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>824</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>3164</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>827</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>221</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>199</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>269 2</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>09</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>144</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>124</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -5679,79 +5679,79 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>980</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>980</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="T41" s="3" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="V41" s="3" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
           <t>185</t>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>113</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>232</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>679</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>280</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>511</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>223</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -6264,12 +6264,12 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>521</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>11111000</t>
+          <t>01011</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>167</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_pre_QA_QC.xlsx
@@ -724,7 +724,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>98</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>192</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>050</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>174</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>885</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2 71</t>
+          <t>1 71</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>5093</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>199</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>144</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>205</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>147</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>186</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>860</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
@@ -2058,17 +2058,17 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>267</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>133</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>00</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>568 8</t>
+          <t>568 1</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>188</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>009</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>382</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>23203</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>103</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>04</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>155</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>14 22</t>
+          <t>14 2</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>183</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>478</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>22848</t>
+          <t>2284</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>260</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>138</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>120</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>625</t>
         </is>
       </c>
       <c r="U32" s="3" t="n">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>106</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>570</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>250</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>847</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>269 2</t>
+          <t>269</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>124</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>235</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>19112</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>270</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>608</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -6264,12 +6264,12 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>01011</t>
+          <t>000</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
